--- a/research/traditional_assets/database/data/thailand/thailand_shoe.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_shoe.xlsx
@@ -1409,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1546,22 +1546,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1021903561584986</v>
+        <v>0.1020219754461816</v>
       </c>
       <c r="C2">
-        <v>53.63361797841368</v>
+        <v>53.22182969784307</v>
       </c>
       <c r="D2">
-        <v>43.66361797841368</v>
+        <v>43.79438732686145</v>
       </c>
       <c r="E2">
-        <v>-14.45576290183782</v>
+        <v>-13.91320527281944</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.5425576290183782</v>
       </c>
       <c r="G2">
         <v>9.970000000000001</v>
@@ -1582,28 +1582,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02729064873962442</v>
       </c>
       <c r="N2">
-        <v>3.776250000000001</v>
+        <v>3.748959351260376</v>
       </c>
       <c r="O2">
-        <v>0.7552500000000002</v>
+        <v>0.7497918702520753</v>
       </c>
       <c r="P2">
-        <v>3.021</v>
+        <v>2.999167481008301</v>
       </c>
       <c r="Q2">
-        <v>5.001</v>
+        <v>4.9791674810083</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1021903561584986</v>
+        <v>0.1026460358042239</v>
       </c>
       <c r="T2">
-        <v>0.8723408754896529</v>
+        <v>0.8793900946855289</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>138.3715732091449</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1628,22 +1628,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1020219754461816</v>
+        <v>0.1018535947338647</v>
       </c>
       <c r="C3">
-        <v>53.22182969784307</v>
+        <v>52.81082705951875</v>
       </c>
       <c r="D3">
-        <v>43.79438732686145</v>
+        <v>43.92594231755551</v>
       </c>
       <c r="E3">
-        <v>-13.91320527281944</v>
+        <v>-13.37064764380106</v>
       </c>
       <c r="F3">
-        <v>0.5425576290183782</v>
+        <v>1.085115258036756</v>
       </c>
       <c r="G3">
         <v>9.970000000000001</v>
@@ -1664,28 +1664,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M3">
-        <v>0.02729064873962442</v>
+        <v>0.05458129747924885</v>
       </c>
       <c r="N3">
-        <v>3.748959351260376</v>
+        <v>3.721668702520752</v>
       </c>
       <c r="O3">
-        <v>0.7497918702520753</v>
+        <v>0.7443337405041504</v>
       </c>
       <c r="P3">
-        <v>2.999167481008301</v>
+        <v>2.977334962016601</v>
       </c>
       <c r="Q3">
-        <v>4.9791674810083</v>
+        <v>4.957334962016601</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1026460358042239</v>
+        <v>0.1031110150345558</v>
       </c>
       <c r="T3">
-        <v>0.8793900946855289</v>
+        <v>0.8865831754976472</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>138.3715732091449</v>
+        <v>69.18578660457247</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1710,22 +1710,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1018535947338647</v>
+        <v>0.1016852140215476</v>
       </c>
       <c r="C4">
-        <v>52.81082705951875</v>
+        <v>52.40061716480044</v>
       </c>
       <c r="D4">
-        <v>43.92594231755551</v>
+        <v>44.05829005185557</v>
       </c>
       <c r="E4">
-        <v>-13.37064764380106</v>
+        <v>-12.82809001478269</v>
       </c>
       <c r="F4">
-        <v>1.085115258036756</v>
+        <v>1.627672887055134</v>
       </c>
       <c r="G4">
         <v>9.970000000000001</v>
@@ -1746,28 +1746,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M4">
-        <v>0.05458129747924885</v>
+        <v>0.08187194621887325</v>
       </c>
       <c r="N4">
-        <v>3.721668702520752</v>
+        <v>3.694378053781127</v>
       </c>
       <c r="O4">
-        <v>0.7443337405041504</v>
+        <v>0.7388756107562255</v>
       </c>
       <c r="P4">
-        <v>2.977334962016601</v>
+        <v>2.955502443024902</v>
       </c>
       <c r="Q4">
-        <v>4.957334962016601</v>
+        <v>4.935502443024902</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1031110150345558</v>
+        <v>0.103585581465513</v>
       </c>
       <c r="T4">
-        <v>0.8865831754976472</v>
+        <v>0.8939245672543452</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>69.18578660457247</v>
+        <v>46.12385773638167</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1792,22 +1792,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1016852140215476</v>
+        <v>0.1015168333092307</v>
       </c>
       <c r="C5">
-        <v>52.40061716480044</v>
+        <v>51.99120720089121</v>
       </c>
       <c r="D5">
-        <v>44.05829005185557</v>
+        <v>44.19143771696473</v>
       </c>
       <c r="E5">
-        <v>-12.82809001478269</v>
+        <v>-12.28553238576431</v>
       </c>
       <c r="F5">
-        <v>1.627672887055134</v>
+        <v>2.170230516073513</v>
       </c>
       <c r="G5">
         <v>9.970000000000001</v>
@@ -1828,28 +1828,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M5">
-        <v>0.08187194621887325</v>
+        <v>0.1091625949584977</v>
       </c>
       <c r="N5">
-        <v>3.694378053781127</v>
+        <v>3.667087405041503</v>
       </c>
       <c r="O5">
-        <v>0.7388756107562255</v>
+        <v>0.7334174810083006</v>
       </c>
       <c r="P5">
-        <v>2.955502443024902</v>
+        <v>2.933669924033202</v>
       </c>
       <c r="Q5">
-        <v>4.935502443024902</v>
+        <v>4.913669924033202</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.103585581465513</v>
+        <v>0.1040700346971153</v>
       </c>
       <c r="T5">
-        <v>0.8939245672543452</v>
+        <v>0.9014189046726414</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.12385773638167</v>
+        <v>34.59289330228624</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1874,22 +1874,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1015168333092307</v>
+        <v>0.1013484525969136</v>
       </c>
       <c r="C6">
-        <v>51.99120720089121</v>
+        <v>51.58260444213881</v>
       </c>
       <c r="D6">
-        <v>44.19143771696473</v>
+        <v>44.3253925872307</v>
       </c>
       <c r="E6">
-        <v>-12.28553238576431</v>
+        <v>-11.74297475674593</v>
       </c>
       <c r="F6">
-        <v>2.170230516073513</v>
+        <v>2.712788145091891</v>
       </c>
       <c r="G6">
         <v>9.970000000000001</v>
@@ -1910,28 +1910,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M6">
-        <v>0.1091625949584977</v>
+        <v>0.1364532436981221</v>
       </c>
       <c r="N6">
-        <v>3.667087405041503</v>
+        <v>3.639796756301878</v>
       </c>
       <c r="O6">
-        <v>0.7334174810083006</v>
+        <v>0.7279593512603757</v>
       </c>
       <c r="P6">
-        <v>2.933669924033202</v>
+        <v>2.911837405041503</v>
       </c>
       <c r="Q6">
-        <v>4.913669924033202</v>
+        <v>4.891837405041503</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1040700346971153</v>
+        <v>0.1045646869441196</v>
       </c>
       <c r="T6">
-        <v>0.9014189046726414</v>
+        <v>0.9090710176155329</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.59289330228624</v>
+        <v>27.67431464182899</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1956,22 +1956,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1013484525969136</v>
+        <v>0.1011800718845967</v>
       </c>
       <c r="C7">
-        <v>51.58260444213881</v>
+        <v>51.17481625136026</v>
       </c>
       <c r="D7">
-        <v>44.3253925872307</v>
+        <v>44.46016202547052</v>
       </c>
       <c r="E7">
-        <v>-11.74297475674593</v>
+        <v>-11.20041712772755</v>
       </c>
       <c r="F7">
-        <v>2.712788145091891</v>
+        <v>3.255345774110269</v>
       </c>
       <c r="G7">
         <v>9.970000000000001</v>
@@ -1992,28 +1992,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M7">
-        <v>0.1364532436981221</v>
+        <v>0.1637438924377465</v>
       </c>
       <c r="N7">
-        <v>3.639796756301878</v>
+        <v>3.612506107562254</v>
       </c>
       <c r="O7">
-        <v>0.7279593512603757</v>
+        <v>0.7225012215124509</v>
       </c>
       <c r="P7">
-        <v>2.911837405041503</v>
+        <v>2.890004886049803</v>
       </c>
       <c r="Q7">
-        <v>4.891837405041503</v>
+        <v>4.870004886049803</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1045646869441196</v>
+        <v>0.1050698637070177</v>
       </c>
       <c r="T7">
-        <v>0.9090710176155329</v>
+        <v>0.9168859414721033</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.67431464182899</v>
+        <v>23.06192886819083</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2038,22 +2038,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1011800718845967</v>
+        <v>0.1010116911722797</v>
       </c>
       <c r="C8">
-        <v>51.17481625136026</v>
+        <v>50.76785008119101</v>
       </c>
       <c r="D8">
-        <v>44.46016202547052</v>
+        <v>44.59575348431966</v>
       </c>
       <c r="E8">
-        <v>-11.20041712772755</v>
+        <v>-10.65785949870917</v>
       </c>
       <c r="F8">
-        <v>3.255345774110269</v>
+        <v>3.797903403128647</v>
       </c>
       <c r="G8">
         <v>9.970000000000001</v>
@@ -2074,28 +2074,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M8">
-        <v>0.1637438924377465</v>
+        <v>0.191034541177371</v>
       </c>
       <c r="N8">
-        <v>3.612506107562254</v>
+        <v>3.585215458822629</v>
       </c>
       <c r="O8">
-        <v>0.7225012215124509</v>
+        <v>0.717043091764526</v>
       </c>
       <c r="P8">
-        <v>2.890004886049803</v>
+        <v>2.868172367058103</v>
       </c>
       <c r="Q8">
-        <v>4.870004886049803</v>
+        <v>4.848172367058103</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1050698637070177</v>
+        <v>0.1055859044863222</v>
       </c>
       <c r="T8">
-        <v>0.9168859414721033</v>
+        <v>0.9248689282073095</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.06192886819083</v>
+        <v>19.76736760130642</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2120,22 +2120,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1010116911722797</v>
+        <v>0.1008433104599627</v>
       </c>
       <c r="C9">
-        <v>50.76785008119102</v>
+        <v>50.36171347545874</v>
       </c>
       <c r="D9">
-        <v>44.59575348431967</v>
+        <v>44.73217450760577</v>
       </c>
       <c r="E9">
-        <v>-10.65785949870917</v>
+        <v>-10.11530186969079</v>
       </c>
       <c r="F9">
-        <v>3.797903403128648</v>
+        <v>4.340461032147026</v>
       </c>
       <c r="G9">
         <v>9.970000000000001</v>
@@ -2156,28 +2156,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M9">
-        <v>0.191034541177371</v>
+        <v>0.2183251899169954</v>
       </c>
       <c r="N9">
-        <v>3.585215458822629</v>
+        <v>3.557924810083005</v>
       </c>
       <c r="O9">
-        <v>0.717043091764526</v>
+        <v>0.711584962016601</v>
       </c>
       <c r="P9">
-        <v>2.868172367058103</v>
+        <v>2.846339848066404</v>
       </c>
       <c r="Q9">
-        <v>4.848172367058103</v>
+        <v>4.826339848066404</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1055859044863222</v>
+        <v>0.1061131635434377</v>
       </c>
       <c r="T9">
-        <v>0.9248689282073095</v>
+        <v>0.9330254581324113</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.76736760130642</v>
+        <v>17.29644665114312</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2202,22 +2202,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1008433104599627</v>
+        <v>0.1006749297476457</v>
       </c>
       <c r="C10">
-        <v>50.36171347545874</v>
+        <v>49.95641407058238</v>
       </c>
       <c r="D10">
-        <v>44.73217450760577</v>
+        <v>44.86943273174778</v>
       </c>
       <c r="E10">
-        <v>-10.11530186969079</v>
+        <v>-9.572744240672417</v>
       </c>
       <c r="F10">
-        <v>4.340461032147026</v>
+        <v>4.883018661165403</v>
       </c>
       <c r="G10">
         <v>9.970000000000001</v>
@@ -2238,28 +2238,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M10">
-        <v>0.2183251899169954</v>
+        <v>0.2456158386566198</v>
       </c>
       <c r="N10">
-        <v>3.557924810083005</v>
+        <v>3.530634161343381</v>
       </c>
       <c r="O10">
-        <v>0.711584962016601</v>
+        <v>0.7061268322686762</v>
       </c>
       <c r="P10">
-        <v>2.846339848066404</v>
+        <v>2.824507329074705</v>
       </c>
       <c r="Q10">
-        <v>4.826339848066404</v>
+        <v>4.804507329074704</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1061131635434377</v>
+        <v>0.1066520107116985</v>
       </c>
       <c r="T10">
-        <v>0.9330254581324113</v>
+        <v>0.9413612524514715</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.29644665114312</v>
+        <v>15.37461924546055</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2284,22 +2284,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1006749297476457</v>
+        <v>0.1005065490353287</v>
       </c>
       <c r="C11">
-        <v>49.95641407058238</v>
+        <v>49.55195959699703</v>
       </c>
       <c r="D11">
-        <v>44.86943273174778</v>
+        <v>45.00753588718081</v>
       </c>
       <c r="E11">
-        <v>-9.572744240672417</v>
+        <v>-9.030186611654038</v>
       </c>
       <c r="F11">
-        <v>4.883018661165403</v>
+        <v>5.425576290183781</v>
       </c>
       <c r="G11">
         <v>9.970000000000001</v>
@@ -2320,28 +2320,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M11">
-        <v>0.2456158386566198</v>
+        <v>0.2729064873962442</v>
       </c>
       <c r="N11">
-        <v>3.530634161343381</v>
+        <v>3.503343512603756</v>
       </c>
       <c r="O11">
-        <v>0.7061268322686762</v>
+        <v>0.7006687025207513</v>
       </c>
       <c r="P11">
-        <v>2.824507329074705</v>
+        <v>2.802674810083005</v>
       </c>
       <c r="Q11">
-        <v>4.804507329074704</v>
+        <v>4.782674810083005</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1066520107116985</v>
+        <v>0.1072028322614763</v>
       </c>
       <c r="T11">
-        <v>0.9413612524514715</v>
+        <v>0.9498822866442886</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.37461924546055</v>
+        <v>13.8371573209145</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1005065490353287</v>
+        <v>0.1004701683230117</v>
       </c>
       <c r="C12">
-        <v>49.55195959699702</v>
+        <v>49.0393526022173</v>
       </c>
       <c r="D12">
-        <v>45.0075358871808</v>
+        <v>45.03748652141946</v>
       </c>
       <c r="E12">
-        <v>-9.030186611654038</v>
+        <v>-8.487628982635659</v>
       </c>
       <c r="F12">
-        <v>5.425576290183782</v>
+        <v>5.968133919202161</v>
       </c>
       <c r="G12">
         <v>9.970000000000001</v>
@@ -2402,45 +2402,45 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M12">
-        <v>0.2729064873962442</v>
+        <v>0.3091493370146719</v>
       </c>
       <c r="N12">
-        <v>3.503343512603756</v>
+        <v>3.467100662985329</v>
       </c>
       <c r="O12">
-        <v>0.7006687025207513</v>
+        <v>0.6934201325970658</v>
       </c>
       <c r="P12">
-        <v>2.802674810083005</v>
+        <v>2.773680530388263</v>
       </c>
       <c r="Q12">
-        <v>4.782674810083005</v>
+        <v>4.753680530388262</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1072028322614763</v>
+        <v>0.1077660318236086</v>
       </c>
       <c r="T12">
-        <v>0.9498822866442889</v>
+        <v>0.9585948047515511</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.8371573209145</v>
+        <v>12.21497039736748</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1004701683230117</v>
+        <v>0.1003137876106947</v>
       </c>
       <c r="C13">
-        <v>49.0393526022173</v>
+        <v>48.6259915403772</v>
       </c>
       <c r="D13">
-        <v>45.03748652141946</v>
+        <v>45.16668308859774</v>
       </c>
       <c r="E13">
-        <v>-8.487628982635659</v>
+        <v>-7.945071353617283</v>
       </c>
       <c r="F13">
-        <v>5.968133919202161</v>
+        <v>6.510691548220538</v>
       </c>
       <c r="G13">
         <v>9.970000000000001</v>
@@ -2484,28 +2484,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M13">
-        <v>0.3091493370146719</v>
+        <v>0.3372538221978238</v>
       </c>
       <c r="N13">
-        <v>3.467100662985329</v>
+        <v>3.438996177802177</v>
       </c>
       <c r="O13">
-        <v>0.6934201325970658</v>
+        <v>0.6877992355604354</v>
       </c>
       <c r="P13">
-        <v>2.773680530388263</v>
+        <v>2.751196942241742</v>
       </c>
       <c r="Q13">
-        <v>4.753680530388262</v>
+        <v>4.731196942241741</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1077660318236086</v>
+        <v>0.1083420313757894</v>
       </c>
       <c r="T13">
-        <v>0.9585948047515511</v>
+        <v>0.9675053346339787</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.21497039736748</v>
+        <v>11.19705619758686</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2530,22 +2530,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1003137876106947</v>
+        <v>0.1001574068983777</v>
       </c>
       <c r="C14">
-        <v>48.6259915403772</v>
+        <v>48.21337384921487</v>
       </c>
       <c r="D14">
-        <v>45.16668308859774</v>
+        <v>45.29662302645379</v>
       </c>
       <c r="E14">
-        <v>-7.945071353617283</v>
+        <v>-7.402513724598903</v>
       </c>
       <c r="F14">
-        <v>6.510691548220538</v>
+        <v>7.053249177238917</v>
       </c>
       <c r="G14">
         <v>9.970000000000001</v>
@@ -2566,28 +2566,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M14">
-        <v>0.3372538221978238</v>
+        <v>0.3653583073809759</v>
       </c>
       <c r="N14">
-        <v>3.438996177802177</v>
+        <v>3.410891692619025</v>
       </c>
       <c r="O14">
-        <v>0.6877992355604354</v>
+        <v>0.6821783385238049</v>
       </c>
       <c r="P14">
-        <v>2.751196942241742</v>
+        <v>2.72871335409522</v>
       </c>
       <c r="Q14">
-        <v>4.731196942241741</v>
+        <v>4.70871335409522</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1083420313757894</v>
+        <v>0.1089312722969858</v>
       </c>
       <c r="T14">
-        <v>0.9675053346339787</v>
+        <v>0.9766207042838182</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.19705619758686</v>
+        <v>10.33574418238787</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2612,22 +2612,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1001574068983777</v>
+        <v>0.1001914261860607</v>
       </c>
       <c r="C15">
-        <v>48.21337384921487</v>
+        <v>47.64248530560467</v>
       </c>
       <c r="D15">
-        <v>45.29662302645379</v>
+        <v>45.26829211186196</v>
       </c>
       <c r="E15">
-        <v>-7.402513724598903</v>
+        <v>-6.859956095580525</v>
       </c>
       <c r="F15">
-        <v>7.053249177238917</v>
+        <v>7.595806806257295</v>
       </c>
       <c r="G15">
         <v>9.970000000000001</v>
@@ -2648,45 +2648,45 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M15">
-        <v>0.3653583073809759</v>
+        <v>0.4063756641347653</v>
       </c>
       <c r="N15">
-        <v>3.410891692619025</v>
+        <v>3.369874335865235</v>
       </c>
       <c r="O15">
-        <v>0.6821783385238049</v>
+        <v>0.6739748671730471</v>
       </c>
       <c r="P15">
-        <v>2.72871335409522</v>
+        <v>2.695899468692188</v>
       </c>
       <c r="Q15">
-        <v>4.70871335409522</v>
+        <v>4.675899468692188</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1089312722969858</v>
+        <v>0.1095342164954194</v>
       </c>
       <c r="T15">
-        <v>0.9766207042838182</v>
+        <v>0.9859480592743519</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.33574418238787</v>
+        <v>9.292510190146851</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2694,22 +2694,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1001914261860607</v>
+        <v>0.1000486454737437</v>
       </c>
       <c r="C16">
-        <v>47.64248530560467</v>
+        <v>47.21907238401005</v>
       </c>
       <c r="D16">
-        <v>45.26829211186196</v>
+        <v>45.38743681928573</v>
       </c>
       <c r="E16">
-        <v>-6.859956095580525</v>
+        <v>-6.317398466562146</v>
       </c>
       <c r="F16">
-        <v>7.595806806257295</v>
+        <v>8.138364435275674</v>
       </c>
       <c r="G16">
         <v>9.970000000000001</v>
@@ -2730,28 +2730,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M16">
-        <v>0.4063756641347653</v>
+        <v>0.4354024972872486</v>
       </c>
       <c r="N16">
-        <v>3.369874335865235</v>
+        <v>3.340847502712752</v>
       </c>
       <c r="O16">
-        <v>0.6739748671730471</v>
+        <v>0.6681695005425504</v>
       </c>
       <c r="P16">
-        <v>2.695899468692188</v>
+        <v>2.672678002170202</v>
       </c>
       <c r="Q16">
-        <v>4.675899468692188</v>
+        <v>4.652678002170202</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1095342164954194</v>
+        <v>0.110151347616169</v>
       </c>
       <c r="T16">
-        <v>0.9859480592743519</v>
+        <v>0.9954948814411333</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.292510190146851</v>
+        <v>8.673009510803727</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1000486454737437</v>
+        <v>0.09990586476142668</v>
       </c>
       <c r="C17">
-        <v>47.21907238401006</v>
+        <v>46.79628828763689</v>
       </c>
       <c r="D17">
-        <v>45.38743681928573</v>
+        <v>45.50721035193094</v>
       </c>
       <c r="E17">
-        <v>-6.317398466562148</v>
+        <v>-5.774840837543769</v>
       </c>
       <c r="F17">
-        <v>8.138364435275673</v>
+        <v>8.680922064294052</v>
       </c>
       <c r="G17">
         <v>9.970000000000001</v>
@@ -2812,28 +2812,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M17">
-        <v>0.4354024972872484</v>
+        <v>0.4644293304397318</v>
       </c>
       <c r="N17">
-        <v>3.340847502712752</v>
+        <v>3.311820669560269</v>
       </c>
       <c r="O17">
-        <v>0.6681695005425504</v>
+        <v>0.6623641339120537</v>
       </c>
       <c r="P17">
-        <v>2.672678002170202</v>
+        <v>2.649456535648215</v>
       </c>
       <c r="Q17">
-        <v>4.652678002170202</v>
+        <v>4.629456535648215</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.110151347616169</v>
+        <v>0.1107831723350318</v>
       </c>
       <c r="T17">
-        <v>0.9954948814411333</v>
+        <v>1.0052690088976</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.673009510803729</v>
+        <v>8.130946416378492</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2858,22 +2858,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09990586476142668</v>
+        <v>0.09976308404910969</v>
       </c>
       <c r="C18">
-        <v>46.79628828763689</v>
+        <v>46.37413800790372</v>
       </c>
       <c r="D18">
-        <v>45.50721035193094</v>
+        <v>45.62761770121615</v>
       </c>
       <c r="E18">
-        <v>-5.774840837543769</v>
+        <v>-5.23228320852539</v>
       </c>
       <c r="F18">
-        <v>8.680922064294052</v>
+        <v>9.223479693312431</v>
       </c>
       <c r="G18">
         <v>9.970000000000001</v>
@@ -2894,28 +2894,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M18">
-        <v>0.4644293304397318</v>
+        <v>0.4934561635922151</v>
       </c>
       <c r="N18">
-        <v>3.311820669560269</v>
+        <v>3.282793836407786</v>
       </c>
       <c r="O18">
-        <v>0.6623641339120537</v>
+        <v>0.6565587672815572</v>
       </c>
       <c r="P18">
-        <v>2.649456535648215</v>
+        <v>2.626235069126229</v>
       </c>
       <c r="Q18">
-        <v>4.629456535648215</v>
+        <v>4.606235069126228</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1107831723350318</v>
+        <v>0.1114302217459153</v>
       </c>
       <c r="T18">
-        <v>1.0052690088976</v>
+        <v>1.015278657497596</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.130946416378492</v>
+        <v>7.652655450709171</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2940,22 +2940,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09976308404910969</v>
+        <v>0.09973550333679268</v>
       </c>
       <c r="C19">
-        <v>46.37413800790372</v>
+        <v>45.85491273178227</v>
       </c>
       <c r="D19">
-        <v>45.62761770121615</v>
+        <v>45.65095005411308</v>
       </c>
       <c r="E19">
-        <v>-5.23228320852539</v>
+        <v>-4.689725579507012</v>
       </c>
       <c r="F19">
-        <v>9.223479693312431</v>
+        <v>9.766037322330808</v>
       </c>
       <c r="G19">
         <v>9.970000000000001</v>
@@ -2976,45 +2976,45 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M19">
-        <v>0.4934561635922151</v>
+        <v>0.5302958266025629</v>
       </c>
       <c r="N19">
-        <v>3.282793836407786</v>
+        <v>3.245954173397438</v>
       </c>
       <c r="O19">
-        <v>0.6565587672815572</v>
+        <v>0.6491908346794876</v>
       </c>
       <c r="P19">
-        <v>2.626235069126229</v>
+        <v>2.59676333871795</v>
       </c>
       <c r="Q19">
-        <v>4.606235069126228</v>
+        <v>4.576763338717949</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1114302217459153</v>
+        <v>0.1120930528497472</v>
       </c>
       <c r="T19">
-        <v>1.015278657497596</v>
+        <v>1.025532443868324</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.652655450709171</v>
+        <v>7.121025304297105</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3022,22 +3022,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09973550333679269</v>
+        <v>0.09959912262447571</v>
       </c>
       <c r="C20">
-        <v>45.85491273178226</v>
+        <v>45.42808020723789</v>
       </c>
       <c r="D20">
-        <v>45.65095005411307</v>
+        <v>45.76667515858708</v>
       </c>
       <c r="E20">
-        <v>-4.689725579507014</v>
+        <v>-4.147167950488635</v>
       </c>
       <c r="F20">
-        <v>9.766037322330806</v>
+        <v>10.30859495134919</v>
       </c>
       <c r="G20">
         <v>9.970000000000001</v>
@@ -3058,28 +3058,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M20">
-        <v>0.5302958266025628</v>
+        <v>0.5597567058582608</v>
       </c>
       <c r="N20">
-        <v>3.245954173397438</v>
+        <v>3.21649329414174</v>
       </c>
       <c r="O20">
-        <v>0.6491908346794877</v>
+        <v>0.643298658828348</v>
       </c>
       <c r="P20">
-        <v>2.59676333871795</v>
+        <v>2.573194635313392</v>
       </c>
       <c r="Q20">
-        <v>4.57676333871795</v>
+        <v>4.553194635313392</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1120930528497472</v>
+        <v>0.1127722501536737</v>
       </c>
       <c r="T20">
-        <v>1.025532443868324</v>
+        <v>1.03603941014944</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.121025304297107</v>
+        <v>6.746234498807785</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3104,22 +3104,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09959912262447571</v>
+        <v>0.09946274191215869</v>
       </c>
       <c r="C21">
-        <v>45.42808020723789</v>
+        <v>45.00183589982963</v>
       </c>
       <c r="D21">
-        <v>45.76667515858708</v>
+        <v>45.88298848019719</v>
       </c>
       <c r="E21">
-        <v>-4.147167950488635</v>
+        <v>-3.604610321470256</v>
       </c>
       <c r="F21">
-        <v>10.30859495134919</v>
+        <v>10.85115258036756</v>
       </c>
       <c r="G21">
         <v>9.970000000000001</v>
@@ -3140,28 +3140,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M21">
-        <v>0.5597567058582608</v>
+        <v>0.5892175851139587</v>
       </c>
       <c r="N21">
-        <v>3.21649329414174</v>
+        <v>3.187032414886042</v>
       </c>
       <c r="O21">
-        <v>0.643298658828348</v>
+        <v>0.6374064829772084</v>
       </c>
       <c r="P21">
-        <v>2.573194635313392</v>
+        <v>2.549625931908833</v>
       </c>
       <c r="Q21">
-        <v>4.553194635313392</v>
+        <v>4.529625931908834</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1127722501536737</v>
+        <v>0.1134684273901984</v>
       </c>
       <c r="T21">
-        <v>1.03603941014944</v>
+        <v>1.046809050587583</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.746234498807785</v>
+        <v>6.408922773867396</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3186,22 +3186,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09946274191215869</v>
+        <v>0.09949436119984172</v>
       </c>
       <c r="C22">
-        <v>45.00183589982963</v>
+        <v>44.43225890825448</v>
       </c>
       <c r="D22">
-        <v>45.88298848019719</v>
+        <v>45.85596911764042</v>
       </c>
       <c r="E22">
-        <v>-3.604610321470256</v>
+        <v>-3.062052692451877</v>
       </c>
       <c r="F22">
-        <v>10.85115258036756</v>
+        <v>11.39371020938594</v>
       </c>
       <c r="G22">
         <v>9.970000000000001</v>
@@ -3222,45 +3222,45 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M22">
-        <v>0.5892175851139587</v>
+        <v>0.6300721745790427</v>
       </c>
       <c r="N22">
-        <v>3.187032414886042</v>
+        <v>3.146177825420958</v>
       </c>
       <c r="O22">
-        <v>0.6374064829772084</v>
+        <v>0.6292355650841917</v>
       </c>
       <c r="P22">
-        <v>2.549625931908833</v>
+        <v>2.516942260336767</v>
       </c>
       <c r="Q22">
-        <v>4.529625931908834</v>
+        <v>4.496942260336766</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1134684273901984</v>
+        <v>0.1141822293668882</v>
       </c>
       <c r="T22">
-        <v>1.046809050587583</v>
+        <v>1.057851340150744</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.408922773867396</v>
+        <v>5.993361002686636</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3268,22 +3268,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09949436119984172</v>
+        <v>0.09936598048752471</v>
       </c>
       <c r="C23">
-        <v>44.43225890825448</v>
+        <v>43.99960353297494</v>
       </c>
       <c r="D23">
-        <v>45.85596911764042</v>
+        <v>45.96587137137927</v>
       </c>
       <c r="E23">
-        <v>-3.062052692451878</v>
+        <v>-2.519495063433499</v>
       </c>
       <c r="F23">
-        <v>11.39371020938594</v>
+        <v>11.93626783840432</v>
       </c>
       <c r="G23">
         <v>9.970000000000001</v>
@@ -3304,28 +3304,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M23">
-        <v>0.6300721745790426</v>
+        <v>0.6600756114637589</v>
       </c>
       <c r="N23">
-        <v>3.146177825420958</v>
+        <v>3.116174388536241</v>
       </c>
       <c r="O23">
-        <v>0.6292355650841917</v>
+        <v>0.6232348777072483</v>
       </c>
       <c r="P23">
-        <v>2.516942260336767</v>
+        <v>2.492939510828993</v>
       </c>
       <c r="Q23">
-        <v>4.496942260336766</v>
+        <v>4.472939510828994</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1141822293668882</v>
+        <v>0.114914333958365</v>
       </c>
       <c r="T23">
-        <v>1.057851340150744</v>
+        <v>1.069176765343729</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.993361002686637</v>
+        <v>5.720935502564517</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3350,22 +3350,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09936598048752471</v>
+        <v>0.09923759977520771</v>
       </c>
       <c r="C24">
-        <v>43.99960353297494</v>
+        <v>43.56747622518643</v>
       </c>
       <c r="D24">
-        <v>45.96587137137927</v>
+        <v>46.07630169260913</v>
       </c>
       <c r="E24">
-        <v>-2.519495063433499</v>
+        <v>-1.976937434415122</v>
       </c>
       <c r="F24">
-        <v>11.93626783840432</v>
+        <v>12.4788254674227</v>
       </c>
       <c r="G24">
         <v>9.970000000000001</v>
@@ -3386,28 +3386,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M24">
-        <v>0.6600756114637589</v>
+        <v>0.6900790483484752</v>
       </c>
       <c r="N24">
-        <v>3.116174388536241</v>
+        <v>3.086170951651525</v>
       </c>
       <c r="O24">
-        <v>0.6232348777072483</v>
+        <v>0.6172341903303051</v>
       </c>
       <c r="P24">
-        <v>2.492939510828993</v>
+        <v>2.46893676132122</v>
       </c>
       <c r="Q24">
-        <v>4.472939510828994</v>
+        <v>4.44893676132122</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.114914333958365</v>
+        <v>0.1156654542535165</v>
       </c>
       <c r="T24">
-        <v>1.069176765343729</v>
+        <v>1.080796357424843</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.720935502564517</v>
+        <v>5.472199176366059</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3432,22 +3432,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09923759977520771</v>
+        <v>0.09910921906289072</v>
       </c>
       <c r="C25">
-        <v>43.56747622518643</v>
+        <v>43.13588080000847</v>
       </c>
       <c r="D25">
-        <v>46.07630169260913</v>
+        <v>46.18726389644954</v>
       </c>
       <c r="E25">
-        <v>-1.976937434415122</v>
+        <v>-1.434379805396743</v>
       </c>
       <c r="F25">
-        <v>12.4788254674227</v>
+        <v>13.02138309644108</v>
       </c>
       <c r="G25">
         <v>9.970000000000001</v>
@@ -3468,28 +3468,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M25">
-        <v>0.6900790483484752</v>
+        <v>0.7200824852331916</v>
       </c>
       <c r="N25">
-        <v>3.086170951651525</v>
+        <v>3.056167514766809</v>
       </c>
       <c r="O25">
-        <v>0.6172341903303051</v>
+        <v>0.6112335029533619</v>
       </c>
       <c r="P25">
-        <v>2.46893676132122</v>
+        <v>2.444934011813447</v>
       </c>
       <c r="Q25">
-        <v>4.44893676132122</v>
+        <v>4.424934011813447</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1156654542535165</v>
+        <v>0.1164363408722246</v>
       </c>
       <c r="T25">
-        <v>1.080796357424843</v>
+        <v>1.092721728244934</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.472199176366059</v>
+        <v>5.244190877350807</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3514,22 +3514,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09910921906289072</v>
+        <v>0.09898083835057371</v>
       </c>
       <c r="C26">
-        <v>43.13588080000847</v>
+        <v>42.70482110939999</v>
       </c>
       <c r="D26">
-        <v>46.18726389644954</v>
+        <v>46.29876183485945</v>
       </c>
       <c r="E26">
-        <v>-1.434379805396745</v>
+        <v>-0.8918221763783656</v>
       </c>
       <c r="F26">
-        <v>13.02138309644108</v>
+        <v>13.56394072545945</v>
       </c>
       <c r="G26">
         <v>9.970000000000001</v>
@@ -3550,28 +3550,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M26">
-        <v>0.7200824852331915</v>
+        <v>0.7500859221179079</v>
       </c>
       <c r="N26">
-        <v>3.056167514766809</v>
+        <v>3.026164077882092</v>
       </c>
       <c r="O26">
-        <v>0.6112335029533619</v>
+        <v>0.6052328155764185</v>
       </c>
       <c r="P26">
-        <v>2.444934011813447</v>
+        <v>2.420931262305674</v>
       </c>
       <c r="Q26">
-        <v>4.424934011813447</v>
+        <v>4.400931262305674</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1164363408722246</v>
+        <v>0.1172277844674316</v>
       </c>
       <c r="T26">
-        <v>1.092721728244934</v>
+        <v>1.10496510895356</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.244190877350808</v>
+        <v>5.034423242256774</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3596,22 +3596,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09898083835057371</v>
+        <v>0.09885245763825672</v>
       </c>
       <c r="C27">
-        <v>42.70482110939999</v>
+        <v>42.27430104260509</v>
       </c>
       <c r="D27">
-        <v>46.29876183485945</v>
+        <v>46.41079939708293</v>
       </c>
       <c r="E27">
-        <v>-0.8918221763783656</v>
+        <v>-0.3492645473599865</v>
       </c>
       <c r="F27">
-        <v>13.56394072545945</v>
+        <v>14.10649835447783</v>
       </c>
       <c r="G27">
         <v>9.970000000000001</v>
@@ -3632,28 +3632,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M27">
-        <v>0.7500859221179079</v>
+        <v>0.7800893590026242</v>
       </c>
       <c r="N27">
-        <v>3.026164077882092</v>
+        <v>2.996160640997376</v>
       </c>
       <c r="O27">
-        <v>0.6052328155764185</v>
+        <v>0.5992321281994752</v>
       </c>
       <c r="P27">
-        <v>2.420931262305674</v>
+        <v>2.396928512797901</v>
       </c>
       <c r="Q27">
-        <v>4.400931262305674</v>
+        <v>4.376928512797901</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1172277844674316</v>
+        <v>0.1180406184300767</v>
       </c>
       <c r="T27">
-        <v>1.10496510895356</v>
+        <v>1.117539391843501</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.034423242256774</v>
+        <v>4.840791579093052</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3678,22 +3678,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09885245763825672</v>
+        <v>0.09872407692593972</v>
       </c>
       <c r="C28">
-        <v>42.27430104260509</v>
+        <v>41.84432452660521</v>
       </c>
       <c r="D28">
-        <v>46.41079939708293</v>
+        <v>46.52338051010142</v>
       </c>
       <c r="E28">
-        <v>-0.3492645473599865</v>
+        <v>0.1932930816583927</v>
       </c>
       <c r="F28">
-        <v>14.10649835447783</v>
+        <v>14.64905598349621</v>
       </c>
       <c r="G28">
         <v>9.970000000000001</v>
@@ -3714,28 +3714,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M28">
-        <v>0.7800893590026242</v>
+        <v>0.8100927958873406</v>
       </c>
       <c r="N28">
-        <v>2.996160640997376</v>
+        <v>2.96615720411266</v>
       </c>
       <c r="O28">
-        <v>0.5992321281994752</v>
+        <v>0.593231440822532</v>
       </c>
       <c r="P28">
-        <v>2.396928512797901</v>
+        <v>2.372925763290128</v>
       </c>
       <c r="Q28">
-        <v>4.376928512797901</v>
+        <v>4.352925763290128</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1180406184300767</v>
+        <v>0.1188757218163558</v>
       </c>
       <c r="T28">
-        <v>1.117539391843501</v>
+        <v>1.130458175634537</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.840791579093052</v>
+        <v>4.661503002089606</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3760,22 +3760,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09872407692593972</v>
+        <v>0.09915569621362273</v>
       </c>
       <c r="C29">
-        <v>41.84432452660521</v>
+        <v>40.92541742074786</v>
       </c>
       <c r="D29">
-        <v>46.52338051010142</v>
+        <v>46.14703103326245</v>
       </c>
       <c r="E29">
-        <v>0.1932930816583927</v>
+        <v>0.73585071067677</v>
       </c>
       <c r="F29">
-        <v>14.64905598349621</v>
+        <v>15.19161361251459</v>
       </c>
       <c r="G29">
         <v>9.970000000000001</v>
@@ -3796,45 +3796,45 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M29">
-        <v>0.8100927958873406</v>
+        <v>0.8780752668033434</v>
       </c>
       <c r="N29">
-        <v>2.96615720411266</v>
+        <v>2.898174733196657</v>
       </c>
       <c r="O29">
-        <v>0.593231440822532</v>
+        <v>0.5796349466393315</v>
       </c>
       <c r="P29">
-        <v>2.372925763290128</v>
+        <v>2.318539786557326</v>
       </c>
       <c r="Q29">
-        <v>4.352925763290128</v>
+        <v>4.298539786557326</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1188757218163558</v>
+        <v>0.1197340225189205</v>
       </c>
       <c r="T29">
-        <v>1.130458175634537</v>
+        <v>1.143735814530878</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.661503002089606</v>
+        <v>4.300599439211561</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3842,22 +3842,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09915569621362273</v>
+        <v>0.09904731550130572</v>
       </c>
       <c r="C30">
-        <v>40.92541742074786</v>
+        <v>40.47678843484723</v>
       </c>
       <c r="D30">
-        <v>46.14703103326245</v>
+        <v>46.2409596763802</v>
       </c>
       <c r="E30">
-        <v>0.73585071067677</v>
+        <v>1.278408339695149</v>
       </c>
       <c r="F30">
-        <v>15.19161361251459</v>
+        <v>15.73417124153297</v>
       </c>
       <c r="G30">
         <v>9.970000000000001</v>
@@ -3878,28 +3878,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M30">
-        <v>0.8780752668033434</v>
+        <v>0.9094350977606057</v>
       </c>
       <c r="N30">
-        <v>2.898174733196657</v>
+        <v>2.866814902239395</v>
       </c>
       <c r="O30">
-        <v>0.5796349466393315</v>
+        <v>0.573362980447879</v>
       </c>
       <c r="P30">
-        <v>2.318539786557326</v>
+        <v>2.293451921791516</v>
       </c>
       <c r="Q30">
-        <v>4.298539786557326</v>
+        <v>4.273451921791516</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1197340225189205</v>
+        <v>0.1206165007060644</v>
       </c>
       <c r="T30">
-        <v>1.143735814530878</v>
+        <v>1.1573874714243</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.300599439211561</v>
+        <v>4.152302906824955</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3924,22 +3924,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09904731550130572</v>
+        <v>0.09893893478898871</v>
       </c>
       <c r="C31">
-        <v>40.47678843484724</v>
+        <v>40.02854259750946</v>
       </c>
       <c r="D31">
-        <v>46.2409596763802</v>
+        <v>46.3352714680608</v>
       </c>
       <c r="E31">
-        <v>1.278408339695146</v>
+        <v>1.820965968713525</v>
       </c>
       <c r="F31">
-        <v>15.73417124153297</v>
+        <v>16.27672887055135</v>
       </c>
       <c r="G31">
         <v>9.970000000000001</v>
@@ -3960,28 +3960,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M31">
-        <v>0.9094350977606055</v>
+        <v>0.9407949287178679</v>
       </c>
       <c r="N31">
-        <v>2.866814902239395</v>
+        <v>2.835455071282133</v>
       </c>
       <c r="O31">
-        <v>0.573362980447879</v>
+        <v>0.5670910142564266</v>
       </c>
       <c r="P31">
-        <v>2.293451921791516</v>
+        <v>2.268364057025706</v>
       </c>
       <c r="Q31">
-        <v>4.273451921791516</v>
+        <v>4.248364057025706</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1206165007060644</v>
+        <v>0.1215241925556982</v>
       </c>
       <c r="T31">
-        <v>1.1573874714243</v>
+        <v>1.171429175657534</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.152302906824956</v>
+        <v>4.013892809930791</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09893893478898871</v>
+        <v>0.09969855407667173</v>
       </c>
       <c r="C32">
-        <v>40.02854259750946</v>
+        <v>38.83295880647012</v>
       </c>
       <c r="D32">
-        <v>46.3352714680608</v>
+        <v>45.68224530603985</v>
       </c>
       <c r="E32">
-        <v>1.820965968713525</v>
+        <v>2.363523597731904</v>
       </c>
       <c r="F32">
-        <v>16.27672887055135</v>
+        <v>16.81928649956972</v>
       </c>
       <c r="G32">
         <v>9.970000000000001</v>
@@ -4042,45 +4042,45 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M32">
-        <v>0.9407949287178679</v>
+        <v>1.031022262423624</v>
       </c>
       <c r="N32">
-        <v>2.835455071282133</v>
+        <v>2.745227737576377</v>
       </c>
       <c r="O32">
-        <v>0.5670910142564266</v>
+        <v>0.5490455475152753</v>
       </c>
       <c r="P32">
-        <v>2.268364057025706</v>
+        <v>2.196182190061101</v>
       </c>
       <c r="Q32">
-        <v>4.248364057025706</v>
+        <v>4.176182190061102</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1215241925556982</v>
+        <v>0.122458194314017</v>
       </c>
       <c r="T32">
-        <v>1.171429175657534</v>
+        <v>1.185877885810572</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.013892809930791</v>
+        <v>3.662627023322629</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4088,22 +4088,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09969855407667173</v>
+        <v>0.09961817336435472</v>
       </c>
       <c r="C33">
-        <v>38.83295880647012</v>
+        <v>38.35863038681343</v>
       </c>
       <c r="D33">
-        <v>45.68224530603985</v>
+        <v>45.75047451540154</v>
       </c>
       <c r="E33">
-        <v>2.363523597731904</v>
+        <v>2.906081226750283</v>
       </c>
       <c r="F33">
-        <v>16.81928649956972</v>
+        <v>17.3618441285881</v>
       </c>
       <c r="G33">
         <v>9.970000000000001</v>
@@ -4124,28 +4124,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M33">
-        <v>1.031022262423624</v>
+        <v>1.064281045082451</v>
       </c>
       <c r="N33">
-        <v>2.745227737576377</v>
+        <v>2.71196895491755</v>
       </c>
       <c r="O33">
-        <v>0.5490455475152753</v>
+        <v>0.54239379098351</v>
       </c>
       <c r="P33">
-        <v>2.196182190061101</v>
+        <v>2.16957516393404</v>
       </c>
       <c r="Q33">
-        <v>4.176182190061102</v>
+        <v>4.14957516393404</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.122458194314017</v>
+        <v>0.1234196667122864</v>
       </c>
       <c r="T33">
-        <v>1.185877885810572</v>
+        <v>1.200751558026934</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.662627023322629</v>
+        <v>3.548169928843797</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4170,22 +4170,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09961817336435472</v>
+        <v>0.1002769926520377</v>
       </c>
       <c r="C34">
-        <v>38.35863038681343</v>
+        <v>37.26278790185744</v>
       </c>
       <c r="D34">
-        <v>45.75047451540154</v>
+        <v>45.19718965946392</v>
       </c>
       <c r="E34">
-        <v>2.906081226750283</v>
+        <v>3.448638855768662</v>
       </c>
       <c r="F34">
-        <v>17.3618441285881</v>
+        <v>17.90440175760648</v>
       </c>
       <c r="G34">
         <v>9.970000000000001</v>
@@ -4206,45 +4206,45 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M34">
-        <v>1.064281045082451</v>
+        <v>1.147672152662575</v>
       </c>
       <c r="N34">
-        <v>2.71196895491755</v>
+        <v>2.628577847337425</v>
       </c>
       <c r="O34">
-        <v>0.54239379098351</v>
+        <v>0.525715569467485</v>
       </c>
       <c r="P34">
-        <v>2.16957516393404</v>
+        <v>2.10286227786994</v>
       </c>
       <c r="Q34">
-        <v>4.14957516393404</v>
+        <v>4.08286227786994</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1234196667122864</v>
+        <v>0.1244098397791608</v>
       </c>
       <c r="T34">
-        <v>1.200751558026934</v>
+        <v>1.21606922045871</v>
       </c>
       <c r="U34">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.548169928843797</v>
+        <v>3.290356040476524</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4252,22 +4252,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1002769926520377</v>
+        <v>0.1002190119397207</v>
       </c>
       <c r="C35">
-        <v>37.26278790185744</v>
+        <v>36.76838559866684</v>
       </c>
       <c r="D35">
-        <v>45.19718965946392</v>
+        <v>45.2453449852917</v>
       </c>
       <c r="E35">
-        <v>3.448638855768662</v>
+        <v>3.991196484787041</v>
       </c>
       <c r="F35">
-        <v>17.90440175760648</v>
+        <v>18.44695938662486</v>
       </c>
       <c r="G35">
         <v>9.970000000000001</v>
@@ -4288,28 +4288,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M35">
-        <v>1.147672152662575</v>
+        <v>1.182450096682654</v>
       </c>
       <c r="N35">
-        <v>2.628577847337425</v>
+        <v>2.593799903317347</v>
       </c>
       <c r="O35">
-        <v>0.525715569467485</v>
+        <v>0.5187599806634694</v>
       </c>
       <c r="P35">
-        <v>2.10286227786994</v>
+        <v>2.075039922653878</v>
       </c>
       <c r="Q35">
-        <v>4.08286227786994</v>
+        <v>4.055039922653878</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1244098397791608</v>
+        <v>0.125430018090486</v>
       </c>
       <c r="T35">
-        <v>1.21606922045871</v>
+        <v>1.231851054479328</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.290356040476524</v>
+        <v>3.193580862815449</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4334,22 +4334,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1002190119397207</v>
+        <v>0.1001610312274037</v>
       </c>
       <c r="C36">
-        <v>36.76838559866684</v>
+        <v>36.27408601906443</v>
       </c>
       <c r="D36">
-        <v>45.2453449852917</v>
+        <v>45.29360303470767</v>
       </c>
       <c r="E36">
-        <v>3.991196484787041</v>
+        <v>4.533754113805417</v>
       </c>
       <c r="F36">
-        <v>18.44695938662486</v>
+        <v>18.98951701564324</v>
       </c>
       <c r="G36">
         <v>9.970000000000001</v>
@@ -4370,28 +4370,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M36">
-        <v>1.182450096682654</v>
+        <v>1.217228040702732</v>
       </c>
       <c r="N36">
-        <v>2.593799903317347</v>
+        <v>2.559021959297269</v>
       </c>
       <c r="O36">
-        <v>0.5187599806634694</v>
+        <v>0.5118043918594538</v>
       </c>
       <c r="P36">
-        <v>2.075039922653878</v>
+        <v>2.047217567437815</v>
       </c>
       <c r="Q36">
-        <v>4.055039922653878</v>
+        <v>4.027217567437814</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.125430018090486</v>
+        <v>0.1264815865036981</v>
       </c>
       <c r="T36">
-        <v>1.231851054479328</v>
+        <v>1.248118483392888</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.193580862815449</v>
+        <v>3.102335695306436</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4416,22 +4416,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1001610312274037</v>
+        <v>0.1001030505150867</v>
       </c>
       <c r="C37">
-        <v>36.27408601906443</v>
+        <v>35.7798894920918</v>
       </c>
       <c r="D37">
-        <v>45.29360303470767</v>
+        <v>45.34196413675342</v>
       </c>
       <c r="E37">
-        <v>4.533754113805417</v>
+        <v>5.076311742823796</v>
       </c>
       <c r="F37">
-        <v>18.98951701564324</v>
+        <v>19.53207464466162</v>
       </c>
       <c r="G37">
         <v>9.970000000000001</v>
@@ -4452,28 +4452,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M37">
-        <v>1.217228040702732</v>
+        <v>1.25200598472281</v>
       </c>
       <c r="N37">
-        <v>2.559021959297269</v>
+        <v>2.524244015277191</v>
       </c>
       <c r="O37">
-        <v>0.5118043918594538</v>
+        <v>0.5048488030554381</v>
       </c>
       <c r="P37">
-        <v>2.047217567437815</v>
+        <v>2.019395212221752</v>
       </c>
       <c r="Q37">
-        <v>4.027217567437814</v>
+        <v>3.999395212221752</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1264815865036981</v>
+        <v>0.127566016429823</v>
       </c>
       <c r="T37">
-        <v>1.248118483392888</v>
+        <v>1.264894269459997</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.102335695306436</v>
+        <v>3.016159703770146</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1001030505150868</v>
+        <v>0.1023538698027698</v>
       </c>
       <c r="C38">
-        <v>35.7798894920918</v>
+        <v>33.43274151803857</v>
       </c>
       <c r="D38">
-        <v>45.34196413675341</v>
+        <v>43.53737379171857</v>
       </c>
       <c r="E38">
-        <v>5.076311742823792</v>
+        <v>5.618869371842171</v>
       </c>
       <c r="F38">
-        <v>19.53207464466161</v>
+        <v>20.07463227367999</v>
       </c>
       <c r="G38">
         <v>9.970000000000001</v>
@@ -4534,45 +4534,45 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M38">
-        <v>1.25200598472281</v>
+        <v>1.443366060477592</v>
       </c>
       <c r="N38">
-        <v>2.524244015277191</v>
+        <v>2.332883939522409</v>
       </c>
       <c r="O38">
-        <v>0.5048488030554382</v>
+        <v>0.4665767879044818</v>
       </c>
       <c r="P38">
-        <v>2.019395212221753</v>
+        <v>1.866307151617927</v>
       </c>
       <c r="Q38">
-        <v>3.999395212221753</v>
+        <v>3.846307151617927</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.127566016429823</v>
+        <v>0.1286848727028091</v>
       </c>
       <c r="T38">
-        <v>1.264894269459997</v>
+        <v>1.282202620164157</v>
       </c>
       <c r="U38">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.016159703770147</v>
+        <v>2.616280168559934</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1023538698027698</v>
+        <v>0.1023582890904527</v>
       </c>
       <c r="C39">
-        <v>33.43274151803857</v>
+        <v>32.8867820149034</v>
       </c>
       <c r="D39">
-        <v>43.53737379171857</v>
+        <v>43.53397191760177</v>
       </c>
       <c r="E39">
-        <v>5.618869371842171</v>
+        <v>6.161427000860551</v>
       </c>
       <c r="F39">
-        <v>20.07463227367999</v>
+        <v>20.61718990269837</v>
       </c>
       <c r="G39">
         <v>9.970000000000001</v>
@@ -4616,28 +4616,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M39">
-        <v>1.443366060477592</v>
+        <v>1.482375954004013</v>
       </c>
       <c r="N39">
-        <v>2.332883939522409</v>
+        <v>2.293874045995988</v>
       </c>
       <c r="O39">
-        <v>0.4665767879044818</v>
+        <v>0.4587748091991976</v>
       </c>
       <c r="P39">
-        <v>1.866307151617927</v>
+        <v>1.83509923679679</v>
       </c>
       <c r="Q39">
-        <v>3.846307151617927</v>
+        <v>3.81509923679679</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1286848727028091</v>
+        <v>0.1298398211136335</v>
       </c>
       <c r="T39">
-        <v>1.282202620164157</v>
+        <v>1.300069304761999</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.616280168559934</v>
+        <v>2.547430690439936</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4662,22 +4662,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1023582890904527</v>
+        <v>0.1035795083781358</v>
       </c>
       <c r="C40">
-        <v>32.8867820149034</v>
+        <v>31.42409668546754</v>
       </c>
       <c r="D40">
-        <v>43.53397191760177</v>
+        <v>42.61384421718429</v>
       </c>
       <c r="E40">
-        <v>6.161427000860551</v>
+        <v>6.70398462987893</v>
       </c>
       <c r="F40">
-        <v>20.61718990269837</v>
+        <v>21.15974753171675</v>
       </c>
       <c r="G40">
         <v>9.970000000000001</v>
@@ -4698,45 +4698,45 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M40">
-        <v>1.482375954004013</v>
+        <v>1.60390886290413</v>
       </c>
       <c r="N40">
-        <v>2.293874045995988</v>
+        <v>2.172341137095871</v>
       </c>
       <c r="O40">
-        <v>0.4587748091991976</v>
+        <v>0.4344682274191742</v>
       </c>
       <c r="P40">
-        <v>1.83509923679679</v>
+        <v>1.737872909676697</v>
       </c>
       <c r="Q40">
-        <v>3.81509923679679</v>
+        <v>3.717872909676696</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1298398211136335</v>
+        <v>0.1310326366854685</v>
       </c>
       <c r="T40">
-        <v>1.300069304761999</v>
+        <v>1.318521782297476</v>
       </c>
       <c r="U40">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.547430690439936</v>
+        <v>2.354404347615179</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1035795083781358</v>
+        <v>0.1036151276658188</v>
       </c>
       <c r="C41">
-        <v>31.42409668546754</v>
+        <v>30.85528511846214</v>
       </c>
       <c r="D41">
-        <v>42.61384421718429</v>
+        <v>42.58759027919727</v>
       </c>
       <c r="E41">
-        <v>6.70398462987893</v>
+        <v>7.246542258897309</v>
       </c>
       <c r="F41">
-        <v>21.15974753171675</v>
+        <v>21.70230516073513</v>
       </c>
       <c r="G41">
         <v>9.970000000000001</v>
@@ -4780,28 +4780,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M41">
-        <v>1.60390886290413</v>
+        <v>1.645034731183723</v>
       </c>
       <c r="N41">
-        <v>2.172341137095871</v>
+        <v>2.131215268816278</v>
       </c>
       <c r="O41">
-        <v>0.4344682274191742</v>
+        <v>0.4262430537632556</v>
       </c>
       <c r="P41">
-        <v>1.737872909676697</v>
+        <v>1.704972215053022</v>
       </c>
       <c r="Q41">
-        <v>3.717872909676696</v>
+        <v>3.684972215053022</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1310326366854685</v>
+        <v>0.1322652127763646</v>
       </c>
       <c r="T41">
-        <v>1.318521782297476</v>
+        <v>1.337589342417468</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.354404347615179</v>
+        <v>2.295544238924799</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1036151276658188</v>
+        <v>0.1036507469535018</v>
       </c>
       <c r="C42">
-        <v>30.85528511846214</v>
+        <v>30.28650588108492</v>
       </c>
       <c r="D42">
-        <v>42.58759027919727</v>
+        <v>42.56136867083843</v>
       </c>
       <c r="E42">
-        <v>7.246542258897309</v>
+        <v>7.789099887915688</v>
       </c>
       <c r="F42">
-        <v>21.70230516073513</v>
+        <v>22.24486278975351</v>
       </c>
       <c r="G42">
         <v>9.970000000000001</v>
@@ -4862,28 +4862,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M42">
-        <v>1.645034731183723</v>
+        <v>1.686160599463316</v>
       </c>
       <c r="N42">
-        <v>2.131215268816278</v>
+        <v>2.090089400536685</v>
       </c>
       <c r="O42">
-        <v>0.4262430537632556</v>
+        <v>0.4180178801073369</v>
       </c>
       <c r="P42">
-        <v>1.704972215053022</v>
+        <v>1.672071520429348</v>
       </c>
       <c r="Q42">
-        <v>3.684972215053022</v>
+        <v>3.652071520429348</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1322652127763646</v>
+        <v>0.1335395711076301</v>
       </c>
       <c r="T42">
-        <v>1.337589342417468</v>
+        <v>1.35730326050763</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.295544238924799</v>
+        <v>2.239555355048584</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4908,22 +4908,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1036507469535018</v>
+        <v>0.1036863662411848</v>
       </c>
       <c r="C43">
-        <v>30.28650588108492</v>
+        <v>29.71775891365562</v>
       </c>
       <c r="D43">
-        <v>42.56136867083843</v>
+        <v>42.53517933242751</v>
       </c>
       <c r="E43">
-        <v>7.789099887915688</v>
+        <v>8.331657516934067</v>
       </c>
       <c r="F43">
-        <v>22.24486278975351</v>
+        <v>22.78742041877189</v>
       </c>
       <c r="G43">
         <v>9.970000000000001</v>
@@ -4944,28 +4944,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M43">
-        <v>1.686160599463316</v>
+        <v>1.727286467742909</v>
       </c>
       <c r="N43">
-        <v>2.090089400536685</v>
+        <v>2.048963532257091</v>
       </c>
       <c r="O43">
-        <v>0.4180178801073369</v>
+        <v>0.4097927064514183</v>
       </c>
       <c r="P43">
-        <v>1.672071520429348</v>
+        <v>1.639170825805673</v>
       </c>
       <c r="Q43">
-        <v>3.652071520429348</v>
+        <v>3.619170825805673</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1335395711076301</v>
+        <v>0.1348578728296289</v>
       </c>
       <c r="T43">
-        <v>1.35730326050763</v>
+        <v>1.377696968876762</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.239555355048584</v>
+        <v>2.186232608499808</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4990,22 +4990,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1036863662411848</v>
+        <v>0.1037219855288678</v>
       </c>
       <c r="C44">
-        <v>29.71775891365564</v>
+        <v>29.14904415664074</v>
       </c>
       <c r="D44">
-        <v>42.53517933242752</v>
+        <v>42.50902220443101</v>
       </c>
       <c r="E44">
-        <v>8.331657516934063</v>
+        <v>8.874215145952443</v>
       </c>
       <c r="F44">
-        <v>22.78742041877188</v>
+        <v>23.32997804779026</v>
       </c>
       <c r="G44">
         <v>9.970000000000001</v>
@@ -5026,28 +5026,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M44">
-        <v>1.727286467742909</v>
+        <v>1.768412336022502</v>
       </c>
       <c r="N44">
-        <v>2.048963532257091</v>
+        <v>2.007837663977498</v>
       </c>
       <c r="O44">
-        <v>0.4097927064514183</v>
+        <v>0.4015675327954997</v>
       </c>
       <c r="P44">
-        <v>1.639170825805673</v>
+        <v>1.606270131181998</v>
       </c>
       <c r="Q44">
-        <v>3.619170825805673</v>
+        <v>3.586270131181998</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1348578728296289</v>
+        <v>0.1362224307523996</v>
       </c>
       <c r="T44">
-        <v>1.377696968876762</v>
+        <v>1.398806245960601</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.186232608499808</v>
+        <v>2.135389989697488</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5072,22 +5072,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1037219855288678</v>
+        <v>0.1037576048165508</v>
       </c>
       <c r="C45">
-        <v>29.14904415664074</v>
+        <v>28.58036155065318</v>
       </c>
       <c r="D45">
-        <v>42.50902220443101</v>
+        <v>42.48289722746182</v>
       </c>
       <c r="E45">
-        <v>8.874215145952443</v>
+        <v>9.416772774970822</v>
       </c>
       <c r="F45">
-        <v>23.32997804779026</v>
+        <v>23.87253567680864</v>
       </c>
       <c r="G45">
         <v>9.970000000000001</v>
@@ -5108,28 +5108,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M45">
-        <v>1.768412336022502</v>
+        <v>1.809538204302095</v>
       </c>
       <c r="N45">
-        <v>2.007837663977498</v>
+        <v>1.966711795697905</v>
       </c>
       <c r="O45">
-        <v>0.4015675327954997</v>
+        <v>0.3933423591395811</v>
       </c>
       <c r="P45">
-        <v>1.606270131181998</v>
+        <v>1.573369436558324</v>
       </c>
       <c r="Q45">
-        <v>3.586270131181998</v>
+        <v>3.553369436558325</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1362224307523996</v>
+        <v>0.1376357228866978</v>
       </c>
       <c r="T45">
-        <v>1.398806245960601</v>
+        <v>1.420669425797435</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.135389989697488</v>
+        <v>2.086858399022545</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5154,22 +5154,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1037576048165508</v>
+        <v>0.1037932241042338</v>
       </c>
       <c r="C46">
-        <v>28.58036155065318</v>
+        <v>28.01171103645163</v>
       </c>
       <c r="D46">
-        <v>42.48289722746182</v>
+        <v>42.45680434227865</v>
       </c>
       <c r="E46">
-        <v>9.416772774970822</v>
+        <v>9.959330403989197</v>
       </c>
       <c r="F46">
-        <v>23.87253567680864</v>
+        <v>24.41509330582702</v>
       </c>
       <c r="G46">
         <v>9.970000000000001</v>
@@ -5190,28 +5190,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M46">
-        <v>1.809538204302095</v>
+        <v>1.850664072581688</v>
       </c>
       <c r="N46">
-        <v>1.966711795697905</v>
+        <v>1.925585927418312</v>
       </c>
       <c r="O46">
-        <v>0.3933423591395811</v>
+        <v>0.3851171854836625</v>
       </c>
       <c r="P46">
-        <v>1.573369436558324</v>
+        <v>1.54046874193465</v>
       </c>
       <c r="Q46">
-        <v>3.553369436558325</v>
+        <v>3.52046874193465</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1376357228866978</v>
+        <v>0.1391004074622432</v>
       </c>
       <c r="T46">
-        <v>1.420669425797435</v>
+        <v>1.443327630355608</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.086858399022545</v>
+        <v>2.040483767933155</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5236,22 +5236,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1037932241042338</v>
+        <v>0.1090544433919168</v>
       </c>
       <c r="C47">
-        <v>28.01171103645163</v>
+        <v>23.93778792667204</v>
       </c>
       <c r="D47">
-        <v>42.45680434227865</v>
+        <v>38.92543886151743</v>
       </c>
       <c r="E47">
-        <v>9.959330403989197</v>
+        <v>10.50188803300758</v>
       </c>
       <c r="F47">
-        <v>24.41509330582702</v>
+        <v>24.9576509348454</v>
       </c>
       <c r="G47">
         <v>9.970000000000001</v>
@@ -5272,45 +5272,45 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M47">
-        <v>1.850664072581688</v>
+        <v>2.246188584136086</v>
       </c>
       <c r="N47">
-        <v>1.925585927418312</v>
+        <v>1.530061415863915</v>
       </c>
       <c r="O47">
-        <v>0.3851171854836625</v>
+        <v>0.306012283172783</v>
       </c>
       <c r="P47">
-        <v>1.54046874193465</v>
+        <v>1.224049132691132</v>
       </c>
       <c r="Q47">
-        <v>3.52046874193465</v>
+        <v>3.204049132691132</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1391004074622432</v>
+        <v>0.1406193396146607</v>
       </c>
       <c r="T47">
-        <v>1.443327630355608</v>
+        <v>1.466825027675194</v>
       </c>
       <c r="U47">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.040483767933155</v>
+        <v>1.681181191405795</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5318,22 +5318,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1090544433919168</v>
+        <v>0.1092036626795998</v>
       </c>
       <c r="C48">
-        <v>23.93778792667204</v>
+        <v>23.30362003392147</v>
       </c>
       <c r="D48">
-        <v>38.92543886151743</v>
+        <v>38.83382859778525</v>
       </c>
       <c r="E48">
-        <v>10.50188803300758</v>
+        <v>11.04444566202596</v>
       </c>
       <c r="F48">
-        <v>24.9576509348454</v>
+        <v>25.50020856386378</v>
       </c>
       <c r="G48">
         <v>9.970000000000001</v>
@@ -5354,28 +5354,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M48">
-        <v>2.246188584136086</v>
+        <v>2.29501877074774</v>
       </c>
       <c r="N48">
-        <v>1.530061415863915</v>
+        <v>1.481231229252261</v>
       </c>
       <c r="O48">
-        <v>0.306012283172783</v>
+        <v>0.2962462458504522</v>
       </c>
       <c r="P48">
-        <v>1.224049132691132</v>
+        <v>1.184984983401809</v>
       </c>
       <c r="Q48">
-        <v>3.204049132691132</v>
+        <v>3.164984983401808</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1406193396146607</v>
+        <v>0.142195589961509</v>
       </c>
       <c r="T48">
-        <v>1.466825027675194</v>
+        <v>1.491209119233256</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.681181191405795</v>
+        <v>1.645411378822693</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5400,22 +5400,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1092036626795998</v>
+        <v>0.1093528819672828</v>
       </c>
       <c r="C49">
-        <v>23.30362003392147</v>
+        <v>22.66988233466888</v>
       </c>
       <c r="D49">
-        <v>38.83382859778525</v>
+        <v>38.74264852755103</v>
       </c>
       <c r="E49">
-        <v>11.04444566202596</v>
+        <v>11.58700329104433</v>
       </c>
       <c r="F49">
-        <v>25.50020856386378</v>
+        <v>26.04276619288215</v>
       </c>
       <c r="G49">
         <v>9.970000000000001</v>
@@ -5436,28 +5436,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M49">
-        <v>2.29501877074774</v>
+        <v>2.343848957359394</v>
       </c>
       <c r="N49">
-        <v>1.481231229252261</v>
+        <v>1.432401042640607</v>
       </c>
       <c r="O49">
-        <v>0.2962462458504522</v>
+        <v>0.2864802085281213</v>
       </c>
       <c r="P49">
-        <v>1.184984983401809</v>
+        <v>1.145920834112485</v>
       </c>
       <c r="Q49">
-        <v>3.164984983401808</v>
+        <v>3.125920834112486</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.142195589961509</v>
+        <v>0.1438324653216976</v>
       </c>
       <c r="T49">
-        <v>1.491209119233256</v>
+        <v>1.516531060466627</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.645411378822693</v>
+        <v>1.61113197509722</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5482,22 +5482,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1093528819672828</v>
+        <v>0.1095021012549658</v>
       </c>
       <c r="C50">
-        <v>22.66988233466888</v>
+        <v>22.03657180578781</v>
       </c>
       <c r="D50">
-        <v>38.74264852755103</v>
+        <v>38.65189562768834</v>
       </c>
       <c r="E50">
-        <v>11.58700329104433</v>
+        <v>12.12956092006271</v>
       </c>
       <c r="F50">
-        <v>26.04276619288215</v>
+        <v>26.58532382190053</v>
       </c>
       <c r="G50">
         <v>9.970000000000001</v>
@@ -5518,28 +5518,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M50">
-        <v>2.343848957359393</v>
+        <v>2.392679143971048</v>
       </c>
       <c r="N50">
-        <v>1.432401042640607</v>
+        <v>1.383570856028953</v>
       </c>
       <c r="O50">
-        <v>0.2864802085281214</v>
+        <v>0.2767141712057906</v>
       </c>
       <c r="P50">
-        <v>1.145920834112486</v>
+        <v>1.106856684823162</v>
       </c>
       <c r="Q50">
-        <v>3.125920834112486</v>
+        <v>3.086856684823162</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1438324653216976</v>
+        <v>0.1455335318724819</v>
       </c>
       <c r="T50">
-        <v>1.516531060466627</v>
+        <v>1.542846019003268</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.611131975097221</v>
+        <v>1.578251730707481</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5564,22 +5564,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1095021012549658</v>
+        <v>0.1096513205426488</v>
       </c>
       <c r="C51">
-        <v>22.03657180578781</v>
+        <v>21.4036854524119</v>
       </c>
       <c r="D51">
-        <v>38.65189562768834</v>
+        <v>38.56156690333081</v>
       </c>
       <c r="E51">
-        <v>12.12956092006271</v>
+        <v>12.67211854908109</v>
       </c>
       <c r="F51">
-        <v>26.58532382190053</v>
+        <v>27.12788145091891</v>
       </c>
       <c r="G51">
         <v>9.970000000000001</v>
@@ -5600,28 +5600,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M51">
-        <v>2.392679143971048</v>
+        <v>2.441509330582702</v>
       </c>
       <c r="N51">
-        <v>1.383570856028953</v>
+        <v>1.334740669417299</v>
       </c>
       <c r="O51">
-        <v>0.2767141712057906</v>
+        <v>0.2669481338834598</v>
       </c>
       <c r="P51">
-        <v>1.106856684823162</v>
+        <v>1.067792535533839</v>
       </c>
       <c r="Q51">
-        <v>3.086856684823162</v>
+        <v>3.047792535533839</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1455335318724819</v>
+        <v>0.1473026410852976</v>
       </c>
       <c r="T51">
-        <v>1.542846019003268</v>
+        <v>1.570213575881375</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.578251730707481</v>
+        <v>1.546686696093332</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5646,22 +5646,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1096513205426488</v>
+        <v>0.1098005398303318</v>
       </c>
       <c r="C52">
-        <v>21.4036854524119</v>
+        <v>20.77122030760522</v>
       </c>
       <c r="D52">
-        <v>38.56156690333081</v>
+        <v>38.47165938754251</v>
       </c>
       <c r="E52">
-        <v>12.67211854908109</v>
+        <v>13.21467617809947</v>
       </c>
       <c r="F52">
-        <v>27.12788145091891</v>
+        <v>27.67043907993729</v>
       </c>
       <c r="G52">
         <v>9.970000000000001</v>
@@ -5682,28 +5682,28 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M52">
-        <v>2.441509330582702</v>
+        <v>2.490339517194356</v>
       </c>
       <c r="N52">
-        <v>1.334740669417299</v>
+        <v>1.285910482805645</v>
       </c>
       <c r="O52">
-        <v>0.2669481338834598</v>
+        <v>0.2571820965611289</v>
       </c>
       <c r="P52">
-        <v>1.067792535533839</v>
+        <v>1.028728386244516</v>
       </c>
       <c r="Q52">
-        <v>3.047792535533839</v>
+        <v>3.008728386244516</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1473026410852976</v>
+        <v>0.1491439588374118</v>
       </c>
       <c r="T52">
-        <v>1.570213575881375</v>
+        <v>1.598698175897364</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.546686696093332</v>
+        <v>1.516359505973854</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5728,22 +5728,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1098005398303318</v>
+        <v>0.1354430102061598</v>
       </c>
       <c r="C53">
-        <v>20.77122030760522</v>
+        <v>9.223807041931554</v>
       </c>
       <c r="D53">
-        <v>38.47165938754251</v>
+        <v>27.46680375088722</v>
       </c>
       <c r="E53">
-        <v>13.21467617809947</v>
+        <v>13.75723380711785</v>
       </c>
       <c r="F53">
-        <v>27.67043907993729</v>
+        <v>28.21299670895567</v>
       </c>
       <c r="G53">
         <v>9.970000000000001</v>
@@ -5764,45 +5764,45 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M53">
-        <v>2.490339517194356</v>
+        <v>4.141667916874693</v>
       </c>
       <c r="N53">
-        <v>1.285910482805645</v>
+        <v>-0.3654179168746921</v>
       </c>
       <c r="O53">
-        <v>0.2571820965611289</v>
+        <v>-0.07308358337493841</v>
       </c>
       <c r="P53">
-        <v>1.028728386244516</v>
+        <v>-0.2923343334997536</v>
       </c>
       <c r="Q53">
-        <v>3.008728386244516</v>
+        <v>1.687665666500246</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1491439588374118</v>
+        <v>0.1521399801479163</v>
       </c>
       <c r="T53">
-        <v>1.598698175897364</v>
+        <v>1.645045672721911</v>
       </c>
       <c r="U53">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.2</v>
+        <v>0.1823540697028923</v>
       </c>
       <c r="W53">
-        <v>0.07199999999999999</v>
+        <v>0.1200304225676154</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.516359505973854</v>
+        <v>0.911770348514461</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5810,22 +5810,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1354430102061598</v>
+        <v>0.1364530102061598</v>
       </c>
       <c r="C54">
-        <v>9.223807041931554</v>
+        <v>8.375231204303141</v>
       </c>
       <c r="D54">
-        <v>27.46680375088722</v>
+        <v>27.16078554227719</v>
       </c>
       <c r="E54">
-        <v>13.75723380711785</v>
+        <v>14.29979143613623</v>
       </c>
       <c r="F54">
-        <v>28.21299670895567</v>
+        <v>28.75555433797405</v>
       </c>
       <c r="G54">
         <v>9.970000000000001</v>
@@ -5846,37 +5846,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M54">
-        <v>4.141667916874693</v>
+        <v>4.221315376814591</v>
       </c>
       <c r="N54">
-        <v>-0.3654179168746921</v>
+        <v>-0.4450653768145902</v>
       </c>
       <c r="O54">
-        <v>-0.07308358337493841</v>
+        <v>-0.08901307536291805</v>
       </c>
       <c r="P54">
-        <v>-0.2923343334997536</v>
+        <v>-0.3560523014516722</v>
       </c>
       <c r="Q54">
-        <v>1.687665666500246</v>
+        <v>1.623947698548328</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1521399801479163</v>
+        <v>0.1544025329170209</v>
       </c>
       <c r="T54">
-        <v>1.645045672721911</v>
+        <v>1.680046644481952</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1823540697028923</v>
+        <v>0.1789134268783094</v>
       </c>
       <c r="W54">
-        <v>0.1200304225676154</v>
+        <v>0.1205355089342642</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.911770348514461</v>
+        <v>0.8945671343915467</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5892,22 +5892,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1364530102061598</v>
+        <v>0.1374630102061598</v>
       </c>
       <c r="C55">
-        <v>8.375231204303141</v>
+        <v>7.533399164200052</v>
       </c>
       <c r="D55">
-        <v>27.16078554227719</v>
+        <v>26.86151113119248</v>
       </c>
       <c r="E55">
-        <v>14.29979143613623</v>
+        <v>14.84234906515461</v>
       </c>
       <c r="F55">
-        <v>28.75555433797405</v>
+        <v>29.29811196699243</v>
       </c>
       <c r="G55">
         <v>9.970000000000001</v>
@@ -5928,37 +5928,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M55">
-        <v>4.221315376814591</v>
+        <v>4.300962836754489</v>
       </c>
       <c r="N55">
-        <v>-0.4450653768145902</v>
+        <v>-0.5247128367544884</v>
       </c>
       <c r="O55">
-        <v>-0.08901307536291805</v>
+        <v>-0.1049425673508977</v>
       </c>
       <c r="P55">
-        <v>-0.3560523014516722</v>
+        <v>-0.4197702694035907</v>
       </c>
       <c r="Q55">
-        <v>1.623947698548328</v>
+        <v>1.560229730596409</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1544025329170209</v>
+        <v>0.1567634575456517</v>
       </c>
       <c r="T55">
-        <v>1.680046644481952</v>
+        <v>1.716569397622864</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1789134268783094</v>
+        <v>0.1756002152694518</v>
       </c>
       <c r="W55">
-        <v>0.1205355089342642</v>
+        <v>0.1210218883984445</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8945671343915467</v>
+        <v>0.8780010763472588</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5974,22 +5974,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1374630102061598</v>
+        <v>0.1384730102061598</v>
       </c>
       <c r="C56">
-        <v>7.533399164200052</v>
+        <v>6.698090429092101</v>
       </c>
       <c r="D56">
-        <v>26.86151113119248</v>
+        <v>26.5687600251029</v>
       </c>
       <c r="E56">
-        <v>14.84234906515461</v>
+        <v>15.38490669417298</v>
       </c>
       <c r="F56">
-        <v>29.29811196699243</v>
+        <v>29.8406695960108</v>
       </c>
       <c r="G56">
         <v>9.970000000000001</v>
@@ -6010,37 +6010,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M56">
-        <v>4.300962836754489</v>
+        <v>4.380610296694386</v>
       </c>
       <c r="N56">
-        <v>-0.5247128367544884</v>
+        <v>-0.6043602966943857</v>
       </c>
       <c r="O56">
-        <v>-0.1049425673508977</v>
+        <v>-0.1208720593388772</v>
       </c>
       <c r="P56">
-        <v>-0.4197702694035907</v>
+        <v>-0.4834882373555086</v>
       </c>
       <c r="Q56">
-        <v>1.560229730596409</v>
+        <v>1.496511762644491</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1567634575456517</v>
+        <v>0.1592293121577773</v>
       </c>
       <c r="T56">
-        <v>1.716569397622864</v>
+        <v>1.754715384236705</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1756002152694518</v>
+        <v>0.1724074840827345</v>
       </c>
       <c r="W56">
-        <v>0.1210218883984445</v>
+        <v>0.1214905813366546</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8780010763472588</v>
+        <v>0.8620374204136723</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6056,22 +6056,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1384730102061598</v>
+        <v>0.1394830102061598</v>
       </c>
       <c r="C57">
-        <v>6.698090429092101</v>
+        <v>5.869094015001572</v>
       </c>
       <c r="D57">
-        <v>26.5687600251029</v>
+        <v>26.28232124003075</v>
       </c>
       <c r="E57">
-        <v>15.38490669417298</v>
+        <v>15.92746432319136</v>
       </c>
       <c r="F57">
-        <v>29.8406695960108</v>
+        <v>30.38322722502918</v>
       </c>
       <c r="G57">
         <v>9.970000000000001</v>
@@ -6092,37 +6092,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M57">
-        <v>4.380610296694386</v>
+        <v>4.460257756634284</v>
       </c>
       <c r="N57">
-        <v>-0.6043602966943857</v>
+        <v>-0.6840077566342839</v>
       </c>
       <c r="O57">
-        <v>-0.1208720593388772</v>
+        <v>-0.1368015513268568</v>
       </c>
       <c r="P57">
-        <v>-0.4834882373555086</v>
+        <v>-0.5472062053074271</v>
       </c>
       <c r="Q57">
-        <v>1.496511762644491</v>
+        <v>1.432793794692573</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1592293121577773</v>
+        <v>0.1618072510704541</v>
       </c>
       <c r="T57">
-        <v>1.754715384236705</v>
+        <v>1.794595279332994</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1724074840827345</v>
+        <v>0.1693287790098285</v>
       </c>
       <c r="W57">
-        <v>0.1214905813366546</v>
+        <v>0.1219425352413572</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8620374204136723</v>
+        <v>0.8466438950491424</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6138,22 +6138,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1394830102061598</v>
+        <v>0.1404930102061598</v>
       </c>
       <c r="C58">
-        <v>5.869094015001572</v>
+        <v>5.046207939410014</v>
       </c>
       <c r="D58">
-        <v>26.28232124003075</v>
+        <v>26.00199279345757</v>
       </c>
       <c r="E58">
-        <v>15.92746432319136</v>
+        <v>16.47002195220974</v>
       </c>
       <c r="F58">
-        <v>30.38322722502918</v>
+        <v>30.92578485404756</v>
       </c>
       <c r="G58">
         <v>9.970000000000001</v>
@@ -6174,37 +6174,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M58">
-        <v>4.460257756634284</v>
+        <v>4.539905216574183</v>
       </c>
       <c r="N58">
-        <v>-0.6840077566342839</v>
+        <v>-0.7636552165741821</v>
       </c>
       <c r="O58">
-        <v>-0.1368015513268568</v>
+        <v>-0.1527310433148364</v>
       </c>
       <c r="P58">
-        <v>-0.5472062053074271</v>
+        <v>-0.6109241732593457</v>
       </c>
       <c r="Q58">
-        <v>1.432793794692573</v>
+        <v>1.369075826740654</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1618072510704541</v>
+        <v>0.1645050941186042</v>
       </c>
       <c r="T58">
-        <v>1.794595279332994</v>
+        <v>1.836330053270971</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1693287790098285</v>
+        <v>0.1663580986763227</v>
       </c>
       <c r="W58">
-        <v>0.1219425352413572</v>
+        <v>0.1223786311143158</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8466438950491424</v>
+        <v>0.8317904933816136</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6220,22 +6220,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1404930102061598</v>
+        <v>0.1415030102061598</v>
       </c>
       <c r="C59">
-        <v>5.046207939410014</v>
+        <v>4.22923874627449</v>
       </c>
       <c r="D59">
-        <v>26.00199279345757</v>
+        <v>25.72758122934043</v>
       </c>
       <c r="E59">
-        <v>16.47002195220974</v>
+        <v>17.01257958122812</v>
       </c>
       <c r="F59">
-        <v>30.92578485404756</v>
+        <v>31.46834248306594</v>
       </c>
       <c r="G59">
         <v>9.970000000000001</v>
@@ -6256,37 +6256,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M59">
-        <v>4.539905216574183</v>
+        <v>4.61955267651408</v>
       </c>
       <c r="N59">
-        <v>-0.7636552165741821</v>
+        <v>-0.8433026765140794</v>
       </c>
       <c r="O59">
-        <v>-0.1527310433148364</v>
+        <v>-0.1686605353028159</v>
       </c>
       <c r="P59">
-        <v>-0.6109241732593457</v>
+        <v>-0.6746421412112635</v>
       </c>
       <c r="Q59">
-        <v>1.369075826740654</v>
+        <v>1.305357858788736</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1645050941186042</v>
+        <v>0.1673314058833329</v>
       </c>
       <c r="T59">
-        <v>1.836330053270971</v>
+        <v>1.88005219739647</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1663580986763227</v>
+        <v>0.1634898555956965</v>
       </c>
       <c r="W59">
-        <v>0.1223786311143158</v>
+        <v>0.1227996891985518</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8317904933816136</v>
+        <v>0.8174492779784824</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6302,22 +6302,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1415030102061598</v>
+        <v>0.1425130102061598</v>
       </c>
       <c r="C60">
-        <v>4.22923874627449</v>
+        <v>3.418001060806169</v>
       </c>
       <c r="D60">
-        <v>25.72758122934042</v>
+        <v>25.45890117289049</v>
       </c>
       <c r="E60">
-        <v>17.01257958122811</v>
+        <v>17.55513721024649</v>
       </c>
       <c r="F60">
-        <v>31.46834248306593</v>
+        <v>32.01090011208431</v>
       </c>
       <c r="G60">
         <v>9.970000000000001</v>
@@ -6338,37 +6338,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M60">
-        <v>4.619552676514079</v>
+        <v>4.699200136453978</v>
       </c>
       <c r="N60">
-        <v>-0.8433026765140785</v>
+        <v>-0.9229501364539776</v>
       </c>
       <c r="O60">
-        <v>-0.1686605353028157</v>
+        <v>-0.1845900272907955</v>
       </c>
       <c r="P60">
-        <v>-0.6746421412112629</v>
+        <v>-0.7383601091631821</v>
       </c>
       <c r="Q60">
-        <v>1.305357858788737</v>
+        <v>1.241639890836818</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1673314058833328</v>
+        <v>0.1702955865146337</v>
       </c>
       <c r="T60">
-        <v>1.880052197396469</v>
+        <v>1.925907129040286</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1634898555956965</v>
+        <v>0.1607188410940745</v>
       </c>
       <c r="W60">
-        <v>0.1227996891985518</v>
+        <v>0.1232064741273899</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8174492779784825</v>
+        <v>0.8035942054703725</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6384,22 +6384,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1425130102061598</v>
+        <v>0.1773609930105669</v>
       </c>
       <c r="C61">
-        <v>3.418001060806169</v>
+        <v>-3.868131012202056</v>
       </c>
       <c r="D61">
-        <v>25.45890117289049</v>
+        <v>18.71532672890064</v>
       </c>
       <c r="E61">
-        <v>17.55513721024649</v>
+        <v>18.09769483926487</v>
       </c>
       <c r="F61">
-        <v>32.01090011208431</v>
+        <v>32.55345774110269</v>
       </c>
       <c r="G61">
         <v>9.970000000000001</v>
@@ -6420,45 +6420,45 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M61">
-        <v>4.699200136453978</v>
+        <v>6.536734314413421</v>
       </c>
       <c r="N61">
-        <v>-0.9229501364539776</v>
+        <v>-2.76048431441342</v>
       </c>
       <c r="O61">
-        <v>-0.1845900272907955</v>
+        <v>-0.552096862882684</v>
       </c>
       <c r="P61">
-        <v>-0.7383601091631821</v>
+        <v>-2.208387451530736</v>
       </c>
       <c r="Q61">
-        <v>1.241639890836818</v>
+        <v>-0.228387451530736</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1702955865146337</v>
+        <v>0.1770029331885171</v>
       </c>
       <c r="T61">
-        <v>1.925907129040286</v>
+        <v>2.029667648893401</v>
       </c>
       <c r="U61">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1607188410940745</v>
+        <v>0.1155393448276891</v>
       </c>
       <c r="W61">
-        <v>0.1232064741273899</v>
+        <v>0.1775996995586</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.8035942054703725</v>
+        <v>0.5776967241384454</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6466,22 +6466,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1773609930105669</v>
+        <v>0.1789109930105669</v>
       </c>
       <c r="C62">
-        <v>-3.868131012202056</v>
+        <v>-4.628617722611125</v>
       </c>
       <c r="D62">
-        <v>18.71532672890064</v>
+        <v>18.49739764750994</v>
       </c>
       <c r="E62">
-        <v>18.09769483926487</v>
+        <v>18.64025246828324</v>
       </c>
       <c r="F62">
-        <v>32.55345774110269</v>
+        <v>33.09601537012107</v>
       </c>
       <c r="G62">
         <v>9.970000000000001</v>
@@ -6502,37 +6502,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M62">
-        <v>6.536734314413421</v>
+        <v>6.64567988632031</v>
       </c>
       <c r="N62">
-        <v>-2.76048431441342</v>
+        <v>-2.869429886320309</v>
       </c>
       <c r="O62">
-        <v>-0.552096862882684</v>
+        <v>-0.5738859772640619</v>
       </c>
       <c r="P62">
-        <v>-2.208387451530736</v>
+        <v>-2.295543909056248</v>
       </c>
       <c r="Q62">
-        <v>-0.228387451530736</v>
+        <v>-0.3155439090562475</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1770029331885171</v>
+        <v>0.1803671109625817</v>
       </c>
       <c r="T62">
-        <v>2.029667648893401</v>
+        <v>2.081710409121437</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1155393448276891</v>
+        <v>0.1136452572075631</v>
       </c>
       <c r="W62">
-        <v>0.1775996995586</v>
+        <v>0.1779800323527214</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5776967241384454</v>
+        <v>0.5682262860378153</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6548,22 +6548,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1789109930105669</v>
+        <v>0.1804609930105668</v>
       </c>
       <c r="C63">
-        <v>-4.628617722611125</v>
+        <v>-5.384087537353473</v>
       </c>
       <c r="D63">
-        <v>18.49739764750994</v>
+        <v>18.28448546178598</v>
       </c>
       <c r="E63">
-        <v>18.64025246828324</v>
+        <v>19.18281009730163</v>
       </c>
       <c r="F63">
-        <v>33.09601537012107</v>
+        <v>33.63857299913945</v>
       </c>
       <c r="G63">
         <v>9.970000000000001</v>
@@ -6584,37 +6584,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M63">
-        <v>6.64567988632031</v>
+        <v>6.754625458227202</v>
       </c>
       <c r="N63">
-        <v>-2.869429886320309</v>
+        <v>-2.978375458227201</v>
       </c>
       <c r="O63">
-        <v>-0.5738859772640619</v>
+        <v>-0.5956750916454403</v>
       </c>
       <c r="P63">
-        <v>-2.295543909056248</v>
+        <v>-2.382700366581761</v>
       </c>
       <c r="Q63">
-        <v>-0.3155439090562475</v>
+        <v>-0.4027003665817612</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1803671109625817</v>
+        <v>0.1839083507247549</v>
       </c>
       <c r="T63">
-        <v>2.081710409121437</v>
+        <v>2.136492261993054</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1136452572075631</v>
+        <v>0.1118122691880862</v>
       </c>
       <c r="W63">
-        <v>0.1779800323527214</v>
+        <v>0.1783480963470323</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5682262860378153</v>
+        <v>0.5590613459404311</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6630,22 +6630,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1804609930105668</v>
+        <v>0.1820109930105669</v>
       </c>
       <c r="C64">
-        <v>-5.384087537353473</v>
+        <v>-6.134711724285943</v>
       </c>
       <c r="D64">
-        <v>18.28448546178598</v>
+        <v>18.07641890387188</v>
       </c>
       <c r="E64">
-        <v>19.18281009730163</v>
+        <v>19.72536772632</v>
       </c>
       <c r="F64">
-        <v>33.63857299913945</v>
+        <v>34.18113062815782</v>
       </c>
       <c r="G64">
         <v>9.970000000000001</v>
@@ -6666,37 +6666,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M64">
-        <v>6.754625458227202</v>
+        <v>6.863571030134091</v>
       </c>
       <c r="N64">
-        <v>-2.978375458227201</v>
+        <v>-3.087321030134091</v>
       </c>
       <c r="O64">
-        <v>-0.5956750916454403</v>
+        <v>-0.6174642060268182</v>
       </c>
       <c r="P64">
-        <v>-2.382700366581761</v>
+        <v>-2.469856824107272</v>
       </c>
       <c r="Q64">
-        <v>-0.4027003665817612</v>
+        <v>-0.4898568241072723</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1839083507247549</v>
+        <v>0.187641008852451</v>
       </c>
       <c r="T64">
-        <v>2.136492261993054</v>
+        <v>2.194235296100974</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1118122691880862</v>
+        <v>0.1100374712644658</v>
       </c>
       <c r="W64">
-        <v>0.1783480963470323</v>
+        <v>0.1787044757700953</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5590613459404311</v>
+        <v>0.5501873563223292</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6712,22 +6712,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1820109930105669</v>
+        <v>0.1835609930105669</v>
       </c>
       <c r="C65">
-        <v>-6.134711724285943</v>
+        <v>-6.880653843272775</v>
       </c>
       <c r="D65">
-        <v>18.07641890387188</v>
+        <v>17.87303441390343</v>
       </c>
       <c r="E65">
-        <v>19.72536772632</v>
+        <v>20.26792535533838</v>
       </c>
       <c r="F65">
-        <v>34.18113062815782</v>
+        <v>34.72368825717621</v>
       </c>
       <c r="G65">
         <v>9.970000000000001</v>
@@ -6748,37 +6748,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M65">
-        <v>6.863571030134091</v>
+        <v>6.972516602040982</v>
       </c>
       <c r="N65">
-        <v>-3.087321030134091</v>
+        <v>-3.196266602040982</v>
       </c>
       <c r="O65">
-        <v>-0.6174642060268182</v>
+        <v>-0.6392533204081964</v>
       </c>
       <c r="P65">
-        <v>-2.469856824107272</v>
+        <v>-2.557013281632785</v>
       </c>
       <c r="Q65">
-        <v>-0.4898568241072723</v>
+        <v>-0.5770132816327851</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.187641008852451</v>
+        <v>0.1915810368761302</v>
       </c>
       <c r="T65">
-        <v>2.194235296100974</v>
+        <v>2.255186276548224</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1100374712644658</v>
+        <v>0.1083181357759585</v>
       </c>
       <c r="W65">
-        <v>0.1787044757700953</v>
+        <v>0.1790497183361875</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5501873563223292</v>
+        <v>0.5415906788797926</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6794,22 +6794,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1835609930105669</v>
+        <v>0.1851109930105669</v>
       </c>
       <c r="C66">
-        <v>-6.880653843272775</v>
+        <v>-7.622070174988423</v>
       </c>
       <c r="D66">
-        <v>17.87303441390343</v>
+        <v>17.67417571120616</v>
       </c>
       <c r="E66">
-        <v>20.26792535533838</v>
+        <v>20.81048298435676</v>
       </c>
       <c r="F66">
-        <v>34.72368825717621</v>
+        <v>35.26624588619458</v>
       </c>
       <c r="G66">
         <v>9.970000000000001</v>
@@ -6830,37 +6830,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M66">
-        <v>6.972516602040982</v>
+        <v>7.081462173947872</v>
       </c>
       <c r="N66">
-        <v>-3.196266602040982</v>
+        <v>-3.305212173947872</v>
       </c>
       <c r="O66">
-        <v>-0.6392533204081964</v>
+        <v>-0.6610424347895744</v>
       </c>
       <c r="P66">
-        <v>-2.557013281632785</v>
+        <v>-2.644169739158297</v>
       </c>
       <c r="Q66">
-        <v>-0.5770132816327851</v>
+        <v>-0.6641697391582975</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1915810368761302</v>
+        <v>0.1957462093583054</v>
       </c>
       <c r="T66">
-        <v>2.255186276548224</v>
+        <v>2.319620170163888</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1083181357759585</v>
+        <v>0.1066517029178669</v>
       </c>
       <c r="W66">
-        <v>0.1790497183361875</v>
+        <v>0.1793843380540923</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5415906788797926</v>
+        <v>0.5332585145893343</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6876,22 +6876,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1851109930105669</v>
+        <v>0.1866609930105669</v>
       </c>
       <c r="C67">
-        <v>-7.622070174988423</v>
+        <v>-8.359110121409714</v>
       </c>
       <c r="D67">
-        <v>17.67417571120616</v>
+        <v>17.47969339380325</v>
       </c>
       <c r="E67">
-        <v>20.81048298435676</v>
+        <v>21.35304061337514</v>
       </c>
       <c r="F67">
-        <v>35.26624588619458</v>
+        <v>35.80880351521296</v>
       </c>
       <c r="G67">
         <v>9.970000000000001</v>
@@ -6912,37 +6912,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M67">
-        <v>7.081462173947872</v>
+        <v>7.190407745854763</v>
       </c>
       <c r="N67">
-        <v>-3.305212173947872</v>
+        <v>-3.414157745854763</v>
       </c>
       <c r="O67">
-        <v>-0.6610424347895744</v>
+        <v>-0.6828315491709526</v>
       </c>
       <c r="P67">
-        <v>-2.644169739158297</v>
+        <v>-2.73132619668381</v>
       </c>
       <c r="Q67">
-        <v>-0.6641697391582975</v>
+        <v>-0.7513261966838103</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1957462093583054</v>
+        <v>0.2001563919864908</v>
       </c>
       <c r="T67">
-        <v>2.319620170163888</v>
+        <v>2.387844292815767</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1066517029178669</v>
+        <v>0.1050357680251719</v>
       </c>
       <c r="W67">
-        <v>0.1793843380540923</v>
+        <v>0.1797088177805455</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5332585145893343</v>
+        <v>0.5251788401258595</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6958,22 +6958,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1866609930105669</v>
+        <v>0.1882109930105669</v>
       </c>
       <c r="C68">
-        <v>-8.359110121409714</v>
+        <v>-9.091916580154205</v>
       </c>
       <c r="D68">
-        <v>17.47969339380325</v>
+        <v>17.28944456407713</v>
       </c>
       <c r="E68">
-        <v>21.35304061337514</v>
+        <v>21.89559824239352</v>
       </c>
       <c r="F68">
-        <v>35.80880351521296</v>
+        <v>36.35136114423134</v>
       </c>
       <c r="G68">
         <v>9.970000000000001</v>
@@ -6994,37 +6994,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M68">
-        <v>7.190407745854763</v>
+        <v>7.299353317761653</v>
       </c>
       <c r="N68">
-        <v>-3.414157745854763</v>
+        <v>-3.523103317761653</v>
       </c>
       <c r="O68">
-        <v>-0.6828315491709526</v>
+        <v>-0.7046206635523307</v>
       </c>
       <c r="P68">
-        <v>-2.73132619668381</v>
+        <v>-2.818482654209322</v>
       </c>
       <c r="Q68">
-        <v>-0.7513261966838103</v>
+        <v>-0.8384826542093222</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2001563919864908</v>
+        <v>0.2048338584103238</v>
       </c>
       <c r="T68">
-        <v>2.387844292815767</v>
+        <v>2.460203210779881</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1050357680251719</v>
+        <v>0.1034680699949455</v>
       </c>
       <c r="W68">
-        <v>0.1797088177805455</v>
+        <v>0.1800236115450149</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5251788401258595</v>
+        <v>0.5173403499747273</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7040,22 +7040,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1882109930105669</v>
+        <v>0.1897609930105669</v>
       </c>
       <c r="C69">
-        <v>-9.091916580154205</v>
+        <v>-9.820626294636135</v>
       </c>
       <c r="D69">
-        <v>17.28944456407713</v>
+        <v>17.10329247861359</v>
       </c>
       <c r="E69">
-        <v>21.89559824239352</v>
+        <v>22.4381558714119</v>
       </c>
       <c r="F69">
-        <v>36.35136114423134</v>
+        <v>36.89391877324972</v>
       </c>
       <c r="G69">
         <v>9.970000000000001</v>
@@ -7076,37 +7076,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M69">
-        <v>7.299353317761653</v>
+        <v>7.408298889668544</v>
       </c>
       <c r="N69">
-        <v>-3.523103317761653</v>
+        <v>-3.632048889668544</v>
       </c>
       <c r="O69">
-        <v>-0.7046206635523307</v>
+        <v>-0.7264097779337089</v>
       </c>
       <c r="P69">
-        <v>-2.818482654209322</v>
+        <v>-2.905639111734835</v>
       </c>
       <c r="Q69">
-        <v>-0.8384826542093222</v>
+        <v>-0.925639111734835</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2048338584103238</v>
+        <v>0.2098036664856465</v>
       </c>
       <c r="T69">
-        <v>2.460203210779881</v>
+        <v>2.537084561116752</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1034680699949455</v>
+        <v>0.1019464807303139</v>
       </c>
       <c r="W69">
-        <v>0.1800236115450149</v>
+        <v>0.180329146669353</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5173403499747273</v>
+        <v>0.5097324036515695</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1897609930105669</v>
+        <v>0.1913109930105669</v>
       </c>
       <c r="C70">
-        <v>-9.820626294636135</v>
+        <v>-10.54537018184276</v>
       </c>
       <c r="D70">
-        <v>17.10329247861359</v>
+        <v>16.92110622042534</v>
       </c>
       <c r="E70">
-        <v>22.4381558714119</v>
+        <v>22.98071350043028</v>
       </c>
       <c r="F70">
-        <v>36.89391877324972</v>
+        <v>37.4364764022681</v>
       </c>
       <c r="G70">
         <v>9.970000000000001</v>
@@ -7158,37 +7158,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M70">
-        <v>7.408298889668544</v>
+        <v>7.517244461575435</v>
       </c>
       <c r="N70">
-        <v>-3.632048889668544</v>
+        <v>-3.740994461575434</v>
       </c>
       <c r="O70">
-        <v>-0.7264097779337089</v>
+        <v>-0.7481988923150868</v>
       </c>
       <c r="P70">
-        <v>-2.905639111734835</v>
+        <v>-2.992795569260347</v>
       </c>
       <c r="Q70">
-        <v>-0.925639111734835</v>
+        <v>-1.012795569260347</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2098036664856465</v>
+        <v>0.2150941073400222</v>
       </c>
       <c r="T70">
-        <v>2.537084561116752</v>
+        <v>2.618925998572131</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1019464807303139</v>
+        <v>0.1004689955023383</v>
       </c>
       <c r="W70">
-        <v>0.180329146669353</v>
+        <v>0.1806258257031305</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5097324036515695</v>
+        <v>0.5023449775116917</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7204,22 +7204,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1913109930105669</v>
+        <v>0.2179412364410513</v>
       </c>
       <c r="C71">
-        <v>-10.54537018184276</v>
+        <v>-13.70562236841893</v>
       </c>
       <c r="D71">
-        <v>16.92110622042534</v>
+        <v>14.30341166286754</v>
       </c>
       <c r="E71">
-        <v>22.98071350043028</v>
+        <v>23.52327112944865</v>
       </c>
       <c r="F71">
-        <v>37.4364764022681</v>
+        <v>37.97903403128647</v>
       </c>
       <c r="G71">
         <v>9.970000000000001</v>
@@ -7240,45 +7240,45 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M71">
-        <v>7.517244461575435</v>
+        <v>8.95545622457735</v>
       </c>
       <c r="N71">
-        <v>-3.740994461575434</v>
+        <v>-5.179206224577349</v>
       </c>
       <c r="O71">
-        <v>-0.7481988923150868</v>
+        <v>-1.03584124491547</v>
       </c>
       <c r="P71">
-        <v>-2.992795569260347</v>
+        <v>-4.14336497966188</v>
       </c>
       <c r="Q71">
-        <v>-1.012795569260347</v>
+        <v>-2.16336497966188</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2150941073400222</v>
+        <v>0.2226713890196375</v>
       </c>
       <c r="T71">
-        <v>2.618925998572131</v>
+        <v>2.736144136291432</v>
       </c>
       <c r="U71">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1004689955023383</v>
+        <v>0.08433406194620129</v>
       </c>
       <c r="W71">
-        <v>0.1806258257031305</v>
+        <v>0.2159140281930857</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.5023449775116917</v>
+        <v>0.4216703097310065</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7286,22 +7286,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2179412364410513</v>
+        <v>0.2198412364410513</v>
       </c>
       <c r="C72">
-        <v>-13.70562236841893</v>
+        <v>-14.40432967044112</v>
       </c>
       <c r="D72">
-        <v>14.30341166286754</v>
+        <v>14.14726198986374</v>
       </c>
       <c r="E72">
-        <v>23.52327112944865</v>
+        <v>24.06582875846703</v>
       </c>
       <c r="F72">
-        <v>37.97903403128647</v>
+        <v>38.52159166030486</v>
       </c>
       <c r="G72">
         <v>9.970000000000001</v>
@@ -7322,37 +7322,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M72">
-        <v>8.95545622457735</v>
+        <v>9.083391313499886</v>
       </c>
       <c r="N72">
-        <v>-5.179206224577349</v>
+        <v>-5.307141313499885</v>
       </c>
       <c r="O72">
-        <v>-1.03584124491547</v>
+        <v>-1.061428262699977</v>
       </c>
       <c r="P72">
-        <v>-4.14336497966188</v>
+        <v>-4.245713050799909</v>
       </c>
       <c r="Q72">
-        <v>-2.16336497966188</v>
+        <v>-2.265713050799909</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2226713890196375</v>
+        <v>0.2287704024341078</v>
       </c>
       <c r="T72">
-        <v>2.736144136291432</v>
+        <v>2.830493934094585</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08433406194620129</v>
+        <v>0.08314625825681815</v>
       </c>
       <c r="W72">
-        <v>0.2159140281930857</v>
+        <v>0.2161941123030423</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4216703097310065</v>
+        <v>0.4157312912840908</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7368,22 +7368,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2198412364410512</v>
+        <v>0.2217412364410512</v>
       </c>
       <c r="C73">
-        <v>-14.40432967044111</v>
+        <v>-15.09966443303242</v>
       </c>
       <c r="D73">
-        <v>14.14726198986374</v>
+        <v>13.99448485629081</v>
       </c>
       <c r="E73">
-        <v>24.06582875846703</v>
+        <v>24.6083863874854</v>
       </c>
       <c r="F73">
-        <v>38.52159166030485</v>
+        <v>39.06414928932323</v>
       </c>
       <c r="G73">
         <v>9.970000000000001</v>
@@ -7404,37 +7404,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M73">
-        <v>9.083391313499884</v>
+        <v>9.211326402422417</v>
       </c>
       <c r="N73">
-        <v>-5.307141313499883</v>
+        <v>-5.435076402422416</v>
       </c>
       <c r="O73">
-        <v>-1.061428262699977</v>
+        <v>-1.087015280484483</v>
       </c>
       <c r="P73">
-        <v>-4.245713050799907</v>
+        <v>-4.348061121937933</v>
       </c>
       <c r="Q73">
-        <v>-2.265713050799907</v>
+        <v>-2.368061121937933</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2287704024341077</v>
+        <v>0.2353050596638972</v>
       </c>
       <c r="T73">
-        <v>2.830493934094584</v>
+        <v>2.93158300316939</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08314625825681816</v>
+        <v>0.08199144911436236</v>
       </c>
       <c r="W73">
-        <v>0.2161941123030423</v>
+        <v>0.2164664162988333</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4157312912840908</v>
+        <v>0.4099572455718119</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7450,22 +7450,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2217412364410512</v>
+        <v>0.2236412364410512</v>
       </c>
       <c r="C74">
-        <v>-15.09966443303242</v>
+        <v>-15.79173474965386</v>
       </c>
       <c r="D74">
-        <v>13.99448485629081</v>
+        <v>13.84497216868775</v>
       </c>
       <c r="E74">
-        <v>24.6083863874854</v>
+        <v>25.15094401650379</v>
       </c>
       <c r="F74">
-        <v>39.06414928932323</v>
+        <v>39.60670691834161</v>
       </c>
       <c r="G74">
         <v>9.970000000000001</v>
@@ -7486,37 +7486,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M74">
-        <v>9.211326402422417</v>
+        <v>9.339261491344951</v>
       </c>
       <c r="N74">
-        <v>-5.435076402422416</v>
+        <v>-5.56301149134495</v>
       </c>
       <c r="O74">
-        <v>-1.087015280484483</v>
+        <v>-1.11260229826899</v>
       </c>
       <c r="P74">
-        <v>-4.348061121937933</v>
+        <v>-4.45040919307596</v>
       </c>
       <c r="Q74">
-        <v>-2.368061121937933</v>
+        <v>-2.47040919307596</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2353050596638972</v>
+        <v>0.2423237655773749</v>
       </c>
       <c r="T74">
-        <v>2.93158300316939</v>
+        <v>3.040160151434923</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08199144911436236</v>
+        <v>0.08086827857854917</v>
       </c>
       <c r="W74">
-        <v>0.2164664162988333</v>
+        <v>0.2167312599111781</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4099572455718119</v>
+        <v>0.404341392892746</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7532,22 +7532,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2236412364410512</v>
+        <v>0.2255412364410512</v>
       </c>
       <c r="C75">
-        <v>-15.79173474965386</v>
+        <v>-16.48064414324983</v>
       </c>
       <c r="D75">
-        <v>13.84497216868775</v>
+        <v>13.69862040411016</v>
       </c>
       <c r="E75">
-        <v>25.15094401650379</v>
+        <v>25.69350164552216</v>
       </c>
       <c r="F75">
-        <v>39.60670691834161</v>
+        <v>40.14926454735998</v>
       </c>
       <c r="G75">
         <v>9.970000000000001</v>
@@ -7568,37 +7568,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M75">
-        <v>9.339261491344951</v>
+        <v>9.467196580267485</v>
       </c>
       <c r="N75">
-        <v>-5.56301149134495</v>
+        <v>-5.690946580267484</v>
       </c>
       <c r="O75">
-        <v>-1.11260229826899</v>
+        <v>-1.138189316053497</v>
       </c>
       <c r="P75">
-        <v>-4.45040919307596</v>
+        <v>-4.552757264213987</v>
       </c>
       <c r="Q75">
-        <v>-2.47040919307596</v>
+        <v>-2.572757264213987</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2423237655773749</v>
+        <v>0.2498823719457355</v>
       </c>
       <c r="T75">
-        <v>3.040160151434923</v>
+        <v>3.157089388028574</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08086827857854917</v>
+        <v>0.07977546400316338</v>
       </c>
       <c r="W75">
-        <v>0.2167312599111781</v>
+        <v>0.2169889455880541</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.404341392892746</v>
+        <v>0.3988773200158169</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7614,22 +7614,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2255412364410512</v>
+        <v>0.2274412364410512</v>
       </c>
       <c r="C76">
-        <v>-16.48064414324983</v>
+        <v>-17.16649180529028</v>
       </c>
       <c r="D76">
-        <v>13.69862040411016</v>
+        <v>13.55533037108808</v>
       </c>
       <c r="E76">
-        <v>25.69350164552216</v>
+        <v>26.23605927454054</v>
       </c>
       <c r="F76">
-        <v>40.14926454735998</v>
+        <v>40.69182217637837</v>
       </c>
       <c r="G76">
         <v>9.970000000000001</v>
@@ -7650,37 +7650,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M76">
-        <v>9.467196580267485</v>
+        <v>9.595131669190019</v>
       </c>
       <c r="N76">
-        <v>-5.690946580267484</v>
+        <v>-5.818881669190018</v>
       </c>
       <c r="O76">
-        <v>-1.138189316053497</v>
+        <v>-1.163776333838004</v>
       </c>
       <c r="P76">
-        <v>-4.552757264213987</v>
+        <v>-4.655105335352014</v>
       </c>
       <c r="Q76">
-        <v>-2.572757264213987</v>
+        <v>-2.675105335352014</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2498823719457355</v>
+        <v>0.2580456668235649</v>
       </c>
       <c r="T76">
-        <v>3.157089388028574</v>
+        <v>3.283372963549717</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07977546400316338</v>
+        <v>0.07871179114978787</v>
       </c>
       <c r="W76">
-        <v>0.2169889455880541</v>
+        <v>0.21723975964688</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3988773200158169</v>
+        <v>0.3935589557489393</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7696,22 +7696,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2274412364410512</v>
+        <v>0.2293412364410513</v>
       </c>
       <c r="C77">
-        <v>-17.16649180529028</v>
+        <v>-17.84937281996559</v>
       </c>
       <c r="D77">
-        <v>13.55533037108808</v>
+        <v>13.41500698543115</v>
       </c>
       <c r="E77">
-        <v>26.23605927454054</v>
+        <v>26.77861690355892</v>
       </c>
       <c r="F77">
-        <v>40.69182217637837</v>
+        <v>41.23437980539674</v>
       </c>
       <c r="G77">
         <v>9.970000000000001</v>
@@ -7732,37 +7732,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M77">
-        <v>9.595131669190019</v>
+        <v>9.723066758112552</v>
       </c>
       <c r="N77">
-        <v>-5.818881669190018</v>
+        <v>-5.946816758112551</v>
       </c>
       <c r="O77">
-        <v>-1.163776333838004</v>
+        <v>-1.18936335162251</v>
       </c>
       <c r="P77">
-        <v>-4.655105335352014</v>
+        <v>-4.757453406490041</v>
       </c>
       <c r="Q77">
-        <v>-2.675105335352014</v>
+        <v>-2.777453406490041</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2580456668235649</v>
+        <v>0.2668892362745468</v>
       </c>
       <c r="T77">
-        <v>3.283372963549717</v>
+        <v>3.42018017036429</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07871179114978787</v>
+        <v>0.07767610968729066</v>
       </c>
       <c r="W77">
-        <v>0.21723975964688</v>
+        <v>0.2174839733357369</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3935589557489393</v>
+        <v>0.3883805484364533</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7778,22 +7778,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2293412364410513</v>
+        <v>0.2312412364410512</v>
       </c>
       <c r="C78">
-        <v>-17.84937281996559</v>
+        <v>-18.52937837459906</v>
       </c>
       <c r="D78">
-        <v>13.41500698543115</v>
+        <v>13.27755905981607</v>
       </c>
       <c r="E78">
-        <v>26.77861690355892</v>
+        <v>27.3211745325773</v>
       </c>
       <c r="F78">
-        <v>41.23437980539674</v>
+        <v>41.77693743441512</v>
       </c>
       <c r="G78">
         <v>9.970000000000001</v>
@@ -7814,37 +7814,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M78">
-        <v>9.723066758112552</v>
+        <v>9.851001847035088</v>
       </c>
       <c r="N78">
-        <v>-5.946816758112551</v>
+        <v>-6.074751847035087</v>
       </c>
       <c r="O78">
-        <v>-1.18936335162251</v>
+        <v>-1.214950369407017</v>
       </c>
       <c r="P78">
-        <v>-4.757453406490041</v>
+        <v>-4.85980147762807</v>
       </c>
       <c r="Q78">
-        <v>-2.777453406490041</v>
+        <v>-2.87980147762807</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2668892362745468</v>
+        <v>0.2765018117647444</v>
       </c>
       <c r="T78">
-        <v>3.42018017036429</v>
+        <v>3.568883656032302</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07767610968729066</v>
+        <v>0.07666732904200114</v>
       </c>
       <c r="W78">
-        <v>0.2174839733357369</v>
+        <v>0.2177218438118961</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3883805484364533</v>
+        <v>0.3833366452100058</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7860,22 +7860,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2312412364410512</v>
+        <v>0.2331412364410513</v>
       </c>
       <c r="C79">
-        <v>-18.52937837459906</v>
+        <v>-19.20659595725552</v>
       </c>
       <c r="D79">
-        <v>13.27755905981607</v>
+        <v>13.14289910617798</v>
       </c>
       <c r="E79">
-        <v>27.3211745325773</v>
+        <v>27.86373216159568</v>
       </c>
       <c r="F79">
-        <v>41.77693743441512</v>
+        <v>42.3194950634335</v>
       </c>
       <c r="G79">
         <v>9.970000000000001</v>
@@ -7896,37 +7896,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M79">
-        <v>9.851001847035088</v>
+        <v>9.97893693595762</v>
       </c>
       <c r="N79">
-        <v>-6.074751847035087</v>
+        <v>-6.202686935957619</v>
       </c>
       <c r="O79">
-        <v>-1.214950369407017</v>
+        <v>-1.240537387191524</v>
       </c>
       <c r="P79">
-        <v>-4.85980147762807</v>
+        <v>-4.962149548766095</v>
       </c>
       <c r="Q79">
-        <v>-2.87980147762807</v>
+        <v>-2.982149548766095</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2765018117647444</v>
+        <v>0.286988257754051</v>
       </c>
       <c r="T79">
-        <v>3.568883656032302</v>
+        <v>3.731105640397407</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07666732904200114</v>
+        <v>0.07568441456710372</v>
       </c>
       <c r="W79">
-        <v>0.2177218438118961</v>
+        <v>0.217953615045077</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3833366452100058</v>
+        <v>0.3784220728355185</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7942,22 +7942,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2331412364410513</v>
+        <v>0.2350412364410512</v>
       </c>
       <c r="C80">
-        <v>-19.20659595725552</v>
+        <v>-19.88110954244583</v>
       </c>
       <c r="D80">
-        <v>13.14289910617798</v>
+        <v>13.01094315000606</v>
       </c>
       <c r="E80">
-        <v>27.86373216159568</v>
+        <v>28.40628979061406</v>
       </c>
       <c r="F80">
-        <v>42.3194950634335</v>
+        <v>42.86205269245188</v>
       </c>
       <c r="G80">
         <v>9.970000000000001</v>
@@ -7978,37 +7978,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M80">
-        <v>9.97893693595762</v>
+        <v>10.10687202488015</v>
       </c>
       <c r="N80">
-        <v>-6.202686935957619</v>
+        <v>-6.330622024880153</v>
       </c>
       <c r="O80">
-        <v>-1.240537387191524</v>
+        <v>-1.266124404976031</v>
       </c>
       <c r="P80">
-        <v>-4.962149548766095</v>
+        <v>-5.064497619904122</v>
       </c>
       <c r="Q80">
-        <v>-2.982149548766095</v>
+        <v>-3.084497619904122</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.286988257754051</v>
+        <v>0.2984734128851963</v>
       </c>
       <c r="T80">
-        <v>3.731105640397407</v>
+        <v>3.908777337559188</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07568441456710372</v>
+        <v>0.07472638400296315</v>
       </c>
       <c r="W80">
-        <v>0.217953615045077</v>
+        <v>0.2181795186521013</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3784220728355185</v>
+        <v>0.3736319200148158</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8024,22 +8024,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2350412364410512</v>
+        <v>0.2369412364410513</v>
       </c>
       <c r="C81">
-        <v>-19.88110954244583</v>
+        <v>-20.55299976575573</v>
       </c>
       <c r="D81">
-        <v>13.01094315000606</v>
+        <v>12.88161055571453</v>
       </c>
       <c r="E81">
-        <v>28.40628979061406</v>
+        <v>28.94884741963244</v>
       </c>
       <c r="F81">
-        <v>42.86205269245188</v>
+        <v>43.40461032147026</v>
       </c>
       <c r="G81">
         <v>9.970000000000001</v>
@@ -8060,37 +8060,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M81">
-        <v>10.10687202488015</v>
+        <v>10.23480711380269</v>
       </c>
       <c r="N81">
-        <v>-6.330622024880153</v>
+        <v>-6.458557113802687</v>
       </c>
       <c r="O81">
-        <v>-1.266124404976031</v>
+        <v>-1.291711422760538</v>
       </c>
       <c r="P81">
-        <v>-5.064497619904122</v>
+        <v>-5.16684569104215</v>
       </c>
       <c r="Q81">
-        <v>-3.084497619904122</v>
+        <v>-3.18684569104215</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2984734128851963</v>
+        <v>0.3111070835294562</v>
       </c>
       <c r="T81">
-        <v>3.908777337559188</v>
+        <v>4.104216204437147</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07472638400296315</v>
+        <v>0.07379230420292611</v>
       </c>
       <c r="W81">
-        <v>0.2181795186521013</v>
+        <v>0.21839977466895</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3736319200148158</v>
+        <v>0.3689615210146305</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2369412364410513</v>
+        <v>0.2388412364410513</v>
       </c>
       <c r="C82">
-        <v>-20.55299976575573</v>
+        <v>-21.22234408816193</v>
       </c>
       <c r="D82">
-        <v>12.88161055571453</v>
+        <v>12.75482386232671</v>
       </c>
       <c r="E82">
-        <v>28.94884741963244</v>
+        <v>29.49140504865081</v>
       </c>
       <c r="F82">
-        <v>43.40461032147026</v>
+        <v>43.94716795048863</v>
       </c>
       <c r="G82">
         <v>9.970000000000001</v>
@@ -8142,37 +8142,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M82">
-        <v>10.23480711380269</v>
+        <v>10.36274220272522</v>
       </c>
       <c r="N82">
-        <v>-6.458557113802687</v>
+        <v>-6.58649220272522</v>
       </c>
       <c r="O82">
-        <v>-1.291711422760538</v>
+        <v>-1.317298440545044</v>
       </c>
       <c r="P82">
-        <v>-5.16684569104215</v>
+        <v>-5.269193762180175</v>
       </c>
       <c r="Q82">
-        <v>-3.18684569104215</v>
+        <v>-3.289193762180175</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3111070835294562</v>
+        <v>0.3250706142415328</v>
       </c>
       <c r="T82">
-        <v>4.104216204437147</v>
+        <v>4.320227583618051</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07379230420292611</v>
+        <v>0.07288128810165542</v>
       </c>
       <c r="W82">
-        <v>0.21839977466895</v>
+        <v>0.2186145922656297</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3689615210146305</v>
+        <v>0.3644064405082772</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8188,22 +8188,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2388412364410513</v>
+        <v>0.2407412364410512</v>
       </c>
       <c r="C83">
-        <v>-21.22234408816193</v>
+        <v>-21.88921695073916</v>
       </c>
       <c r="D83">
-        <v>12.75482386232671</v>
+        <v>12.63050862876785</v>
       </c>
       <c r="E83">
-        <v>29.49140504865081</v>
+        <v>30.03396267766919</v>
       </c>
       <c r="F83">
-        <v>43.94716795048863</v>
+        <v>44.48972557950702</v>
       </c>
       <c r="G83">
         <v>9.970000000000001</v>
@@ -8224,37 +8224,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M83">
-        <v>10.36274220272522</v>
+        <v>10.49067729164775</v>
       </c>
       <c r="N83">
-        <v>-6.58649220272522</v>
+        <v>-6.714427291647754</v>
       </c>
       <c r="O83">
-        <v>-1.317298440545044</v>
+        <v>-1.342885458329551</v>
       </c>
       <c r="P83">
-        <v>-5.269193762180175</v>
+        <v>-5.371541833318203</v>
       </c>
       <c r="Q83">
-        <v>-3.289193762180175</v>
+        <v>-3.391541833318203</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3250706142415328</v>
+        <v>0.3405856483660624</v>
       </c>
       <c r="T83">
-        <v>4.320227583618051</v>
+        <v>4.560240227152387</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07288128810165542</v>
+        <v>0.07199249190529376</v>
       </c>
       <c r="W83">
-        <v>0.2186145922656297</v>
+        <v>0.2188241704087317</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3644064405082772</v>
+        <v>0.3599624595264689</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8270,22 +8270,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2407412364410512</v>
+        <v>0.2426412364410513</v>
       </c>
       <c r="C84">
-        <v>-21.88921695073916</v>
+        <v>-22.55368992040745</v>
       </c>
       <c r="D84">
-        <v>12.63050862876785</v>
+        <v>12.50859328811794</v>
       </c>
       <c r="E84">
-        <v>30.03396267766919</v>
+        <v>30.57652030668757</v>
       </c>
       <c r="F84">
-        <v>44.48972557950702</v>
+        <v>45.03228320852539</v>
       </c>
       <c r="G84">
         <v>9.970000000000001</v>
@@ -8306,37 +8306,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M84">
-        <v>10.49067729164775</v>
+        <v>10.61861238057029</v>
       </c>
       <c r="N84">
-        <v>-6.714427291647754</v>
+        <v>-6.842362380570288</v>
       </c>
       <c r="O84">
-        <v>-1.342885458329551</v>
+        <v>-1.368472476114058</v>
       </c>
       <c r="P84">
-        <v>-5.371541833318203</v>
+        <v>-5.473889904456231</v>
       </c>
       <c r="Q84">
-        <v>-3.391541833318203</v>
+        <v>-3.493889904456231</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3405856483660624</v>
+        <v>0.3579259806228897</v>
       </c>
       <c r="T84">
-        <v>4.560240227152387</v>
+        <v>4.828489652278998</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07199249190529376</v>
+        <v>0.07112511248474805</v>
       </c>
       <c r="W84">
-        <v>0.2188241704087317</v>
+        <v>0.2190286984760964</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3599624595264689</v>
+        <v>0.3556255624237403</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8352,22 +8352,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2426412364410513</v>
+        <v>0.2445412364410512</v>
       </c>
       <c r="C85">
-        <v>-22.55368992040745</v>
+        <v>-23.21583182731912</v>
       </c>
       <c r="D85">
-        <v>12.50859328811794</v>
+        <v>12.38900901022466</v>
       </c>
       <c r="E85">
-        <v>30.57652030668757</v>
+        <v>31.11907793570595</v>
       </c>
       <c r="F85">
-        <v>45.03228320852539</v>
+        <v>45.57484083754377</v>
       </c>
       <c r="G85">
         <v>9.970000000000001</v>
@@ -8388,37 +8388,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M85">
-        <v>10.61861238057029</v>
+        <v>10.74654746949282</v>
       </c>
       <c r="N85">
-        <v>-6.842362380570288</v>
+        <v>-6.970297469492822</v>
       </c>
       <c r="O85">
-        <v>-1.368472476114058</v>
+        <v>-1.394059493898564</v>
       </c>
       <c r="P85">
-        <v>-5.473889904456231</v>
+        <v>-5.576237975594258</v>
       </c>
       <c r="Q85">
-        <v>-3.493889904456231</v>
+        <v>-3.596237975594258</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3579259806228897</v>
+        <v>0.3774338544118203</v>
       </c>
       <c r="T85">
-        <v>4.828489652278998</v>
+        <v>5.130270255546437</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07112511248474805</v>
+        <v>0.07027838495516772</v>
       </c>
       <c r="W85">
-        <v>0.2190286984760964</v>
+        <v>0.2192283568275715</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3556255624237403</v>
+        <v>0.3513919247758386</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8434,22 +8434,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2445412364410513</v>
+        <v>0.2464412364410512</v>
       </c>
       <c r="C86">
-        <v>-23.21583182731912</v>
+        <v>-23.87570889443985</v>
       </c>
       <c r="D86">
-        <v>12.38900901022465</v>
+        <v>12.27168957212229</v>
       </c>
       <c r="E86">
-        <v>31.11907793570595</v>
+        <v>31.66163556472432</v>
       </c>
       <c r="F86">
-        <v>45.57484083754377</v>
+        <v>46.11739846656214</v>
       </c>
       <c r="G86">
         <v>9.970000000000001</v>
@@ -8470,37 +8470,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M86">
-        <v>10.74654746949282</v>
+        <v>10.87448255841535</v>
       </c>
       <c r="N86">
-        <v>-6.97029746949282</v>
+        <v>-7.098232558415352</v>
       </c>
       <c r="O86">
-        <v>-1.394059493898564</v>
+        <v>-1.419646511683071</v>
       </c>
       <c r="P86">
-        <v>-5.576237975594256</v>
+        <v>-5.678586046732282</v>
       </c>
       <c r="Q86">
-        <v>-3.596237975594256</v>
+        <v>-3.698586046732282</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3774338544118201</v>
+        <v>0.3995427780392748</v>
       </c>
       <c r="T86">
-        <v>5.130270255546433</v>
+        <v>5.472288272582862</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07027838495516774</v>
+        <v>0.06945158042628341</v>
       </c>
       <c r="W86">
-        <v>0.2192283568275715</v>
+        <v>0.2194233173354824</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3513919247758387</v>
+        <v>0.3472579021314171</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8516,22 +8516,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2464412364410512</v>
+        <v>0.2483412364410512</v>
       </c>
       <c r="C87">
-        <v>-23.87570889443985</v>
+        <v>-24.53338485983621</v>
       </c>
       <c r="D87">
-        <v>12.27168957212229</v>
+        <v>12.15657123574431</v>
       </c>
       <c r="E87">
-        <v>31.66163556472432</v>
+        <v>32.2041931937427</v>
       </c>
       <c r="F87">
-        <v>46.11739846656214</v>
+        <v>46.65995609558053</v>
       </c>
       <c r="G87">
         <v>9.970000000000001</v>
@@ -8552,37 +8552,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M87">
-        <v>10.87448255841535</v>
+        <v>11.00241764733789</v>
       </c>
       <c r="N87">
-        <v>-7.098232558415352</v>
+        <v>-7.226167647337887</v>
       </c>
       <c r="O87">
-        <v>-1.419646511683071</v>
+        <v>-1.445233529467577</v>
       </c>
       <c r="P87">
-        <v>-5.678586046732282</v>
+        <v>-5.780934117870309</v>
       </c>
       <c r="Q87">
-        <v>-3.698586046732282</v>
+        <v>-3.800934117870309</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3995427780392748</v>
+        <v>0.4248101193277944</v>
       </c>
       <c r="T87">
-        <v>5.472288272582862</v>
+        <v>5.863166006338782</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06945158042628341</v>
+        <v>0.06864400390969871</v>
       </c>
       <c r="W87">
-        <v>0.2194233173354824</v>
+        <v>0.219613743878093</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3472579021314171</v>
+        <v>0.3432200195484936</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8598,22 +8598,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2483412364410512</v>
+        <v>0.2502412364410513</v>
       </c>
       <c r="C88">
-        <v>-24.53338485983621</v>
+        <v>-25.18892109214421</v>
       </c>
       <c r="D88">
-        <v>12.15657123574431</v>
+        <v>12.04359263245469</v>
       </c>
       <c r="E88">
-        <v>32.2041931937427</v>
+        <v>32.74675082276108</v>
       </c>
       <c r="F88">
-        <v>46.65995609558053</v>
+        <v>47.2025137245989</v>
       </c>
       <c r="G88">
         <v>9.970000000000001</v>
@@ -8634,37 +8634,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M88">
-        <v>11.00241764733789</v>
+        <v>11.13035273626042</v>
       </c>
       <c r="N88">
-        <v>-7.226167647337887</v>
+        <v>-7.354102736260421</v>
       </c>
       <c r="O88">
-        <v>-1.445233529467577</v>
+        <v>-1.470820547252084</v>
       </c>
       <c r="P88">
-        <v>-5.780934117870309</v>
+        <v>-5.883282189008336</v>
       </c>
       <c r="Q88">
-        <v>-3.800934117870309</v>
+        <v>-3.903282189008336</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4248101193277944</v>
+        <v>0.453964743891471</v>
       </c>
       <c r="T88">
-        <v>5.863166006338782</v>
+        <v>6.314178776057149</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06864400390969871</v>
+        <v>0.06785499237050678</v>
       </c>
       <c r="W88">
-        <v>0.219613743878093</v>
+        <v>0.2197997927990345</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3432200195484936</v>
+        <v>0.3392749618525339</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8680,22 +8680,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2502412364410513</v>
+        <v>0.2521412364410512</v>
       </c>
       <c r="C89">
-        <v>-25.18892109214421</v>
+        <v>-25.84237669965852</v>
       </c>
       <c r="D89">
-        <v>12.04359263245469</v>
+        <v>11.93269465395876</v>
       </c>
       <c r="E89">
-        <v>32.74675082276108</v>
+        <v>33.28930845177946</v>
       </c>
       <c r="F89">
-        <v>47.2025137245989</v>
+        <v>47.74507135361728</v>
       </c>
       <c r="G89">
         <v>9.970000000000001</v>
@@ -8716,37 +8716,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M89">
-        <v>11.13035273626042</v>
+        <v>11.25828782518296</v>
       </c>
       <c r="N89">
-        <v>-7.354102736260421</v>
+        <v>-7.482037825182955</v>
       </c>
       <c r="O89">
-        <v>-1.470820547252084</v>
+        <v>-1.496407565036591</v>
       </c>
       <c r="P89">
-        <v>-5.883282189008336</v>
+        <v>-5.985630260146364</v>
       </c>
       <c r="Q89">
-        <v>-3.903282189008336</v>
+        <v>-4.005630260146363</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.453964743891471</v>
+        <v>0.4879784725490936</v>
       </c>
       <c r="T89">
-        <v>6.314178776057149</v>
+        <v>6.840360340728579</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06785499237050678</v>
+        <v>0.06708391291175102</v>
       </c>
       <c r="W89">
-        <v>0.2197997927990345</v>
+        <v>0.2199816133354091</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3392749618525339</v>
+        <v>0.3354195645587551</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8762,22 +8762,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2521412364410512</v>
+        <v>0.2540412364410513</v>
       </c>
       <c r="C90">
-        <v>-25.84237669965852</v>
+        <v>-26.49380863344958</v>
       </c>
       <c r="D90">
-        <v>11.93269465395876</v>
+        <v>11.82382034918609</v>
       </c>
       <c r="E90">
-        <v>33.28930845177946</v>
+        <v>33.83186608079784</v>
       </c>
       <c r="F90">
-        <v>47.74507135361728</v>
+        <v>48.28762898263566</v>
       </c>
       <c r="G90">
         <v>9.970000000000001</v>
@@ -8798,37 +8798,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M90">
-        <v>11.25828782518296</v>
+        <v>11.38622291410549</v>
       </c>
       <c r="N90">
-        <v>-7.482037825182955</v>
+        <v>-7.609972914105487</v>
       </c>
       <c r="O90">
-        <v>-1.496407565036591</v>
+        <v>-1.521994582821097</v>
       </c>
       <c r="P90">
-        <v>-5.985630260146364</v>
+        <v>-6.08797833128439</v>
       </c>
       <c r="Q90">
-        <v>-4.005630260146363</v>
+        <v>-4.107978331284389</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4879784725490936</v>
+        <v>0.5281765155081021</v>
       </c>
       <c r="T90">
-        <v>6.840360340728579</v>
+        <v>7.462211280794813</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06708391291175102</v>
+        <v>0.06633016108128191</v>
       </c>
       <c r="W90">
-        <v>0.2199816133354091</v>
+        <v>0.2201593480170337</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3354195645587551</v>
+        <v>0.3316508054064096</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2540412364410513</v>
+        <v>0.2559412364410512</v>
       </c>
       <c r="C91">
-        <v>-26.49380863344958</v>
+        <v>-27.1432717848867</v>
       </c>
       <c r="D91">
-        <v>11.82382034918609</v>
+        <v>11.71691482676733</v>
       </c>
       <c r="E91">
-        <v>33.83186608079784</v>
+        <v>34.37442370981621</v>
       </c>
       <c r="F91">
-        <v>48.28762898263566</v>
+        <v>48.83018661165404</v>
       </c>
       <c r="G91">
         <v>9.970000000000001</v>
@@ -8880,37 +8880,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M91">
-        <v>11.38622291410549</v>
+        <v>11.51415800302802</v>
       </c>
       <c r="N91">
-        <v>-7.609972914105487</v>
+        <v>-7.737908003028021</v>
       </c>
       <c r="O91">
-        <v>-1.521994582821097</v>
+        <v>-1.547581600605604</v>
       </c>
       <c r="P91">
-        <v>-6.08797833128439</v>
+        <v>-6.190326402422417</v>
       </c>
       <c r="Q91">
-        <v>-4.107978331284389</v>
+        <v>-4.210326402422417</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5281765155081021</v>
+        <v>0.5764141670589122</v>
       </c>
       <c r="T91">
-        <v>7.462211280794813</v>
+        <v>8.208432408874295</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06633016108128191</v>
+        <v>0.06559315929148989</v>
       </c>
       <c r="W91">
-        <v>0.2201593480170337</v>
+        <v>0.2203331330390667</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3316508054064096</v>
+        <v>0.3279657964574495</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8926,22 +8926,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2559412364410512</v>
+        <v>0.2578412364410512</v>
       </c>
       <c r="C92">
-        <v>-27.1432717848867</v>
+        <v>-27.79081907791814</v>
       </c>
       <c r="D92">
-        <v>11.71691482676733</v>
+        <v>11.61192516275428</v>
       </c>
       <c r="E92">
-        <v>34.37442370981621</v>
+        <v>34.9169813388346</v>
       </c>
       <c r="F92">
-        <v>48.83018661165404</v>
+        <v>49.37274424067242</v>
       </c>
       <c r="G92">
         <v>9.970000000000001</v>
@@ -8962,37 +8962,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M92">
-        <v>11.51415800302802</v>
+        <v>11.64209309195056</v>
       </c>
       <c r="N92">
-        <v>-7.737908003028021</v>
+        <v>-7.865843091950556</v>
       </c>
       <c r="O92">
-        <v>-1.547581600605604</v>
+        <v>-1.573168618390111</v>
       </c>
       <c r="P92">
-        <v>-6.190326402422417</v>
+        <v>-6.292674473560444</v>
       </c>
       <c r="Q92">
-        <v>-4.210326402422417</v>
+        <v>-4.312674473560444</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5764141670589122</v>
+        <v>0.6353712967321248</v>
       </c>
       <c r="T92">
-        <v>8.208432408874295</v>
+        <v>9.120480454304774</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06559315929148989</v>
+        <v>0.06487235534323176</v>
       </c>
       <c r="W92">
-        <v>0.2203331330390667</v>
+        <v>0.220503098610066</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3279657964574495</v>
+        <v>0.3243617767161587</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9008,22 +9008,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2578412364410512</v>
+        <v>0.2597412364410513</v>
       </c>
       <c r="C93">
-        <v>-27.79081907791814</v>
+        <v>-28.43650155643374</v>
       </c>
       <c r="D93">
-        <v>11.61192516275428</v>
+        <v>11.50880031325705</v>
       </c>
       <c r="E93">
-        <v>34.9169813388346</v>
+        <v>35.45953896785297</v>
       </c>
       <c r="F93">
-        <v>49.37274424067242</v>
+        <v>49.91530186969079</v>
       </c>
       <c r="G93">
         <v>9.970000000000001</v>
@@ -9044,37 +9044,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M93">
-        <v>11.64209309195056</v>
+        <v>11.77002818087309</v>
       </c>
       <c r="N93">
-        <v>-7.865843091950556</v>
+        <v>-7.993778180873088</v>
       </c>
       <c r="O93">
-        <v>-1.573168618390111</v>
+        <v>-1.598755636174618</v>
       </c>
       <c r="P93">
-        <v>-6.292674473560444</v>
+        <v>-6.39502254469847</v>
       </c>
       <c r="Q93">
-        <v>-4.312674473560444</v>
+        <v>-4.41502254469847</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6353712967321248</v>
+        <v>0.7090677088236406</v>
       </c>
       <c r="T93">
-        <v>9.120480454304774</v>
+        <v>10.26054051109287</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06487235534323176</v>
+        <v>0.06416722104602272</v>
       </c>
       <c r="W93">
-        <v>0.220503098610066</v>
+        <v>0.2206693692773479</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3243617767161587</v>
+        <v>0.3208361052301136</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9090,22 +9090,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2597412364410513</v>
+        <v>0.2616412364410513</v>
       </c>
       <c r="C94">
-        <v>-28.43650155643374</v>
+        <v>-29.08036846701362</v>
       </c>
       <c r="D94">
-        <v>11.50880031325705</v>
+        <v>11.40749103169555</v>
       </c>
       <c r="E94">
-        <v>35.45953896785297</v>
+        <v>36.00209659687135</v>
       </c>
       <c r="F94">
-        <v>49.91530186969079</v>
+        <v>50.45785949870918</v>
       </c>
       <c r="G94">
         <v>9.970000000000001</v>
@@ -9126,37 +9126,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M94">
-        <v>11.77002818087309</v>
+        <v>11.89796326979562</v>
       </c>
       <c r="N94">
-        <v>-7.993778180873088</v>
+        <v>-8.121713269795624</v>
       </c>
       <c r="O94">
-        <v>-1.598755636174618</v>
+        <v>-1.624342653959125</v>
       </c>
       <c r="P94">
-        <v>-6.39502254469847</v>
+        <v>-6.497370615836499</v>
       </c>
       <c r="Q94">
-        <v>-4.41502254469847</v>
+        <v>-4.5173706158365</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7090677088236406</v>
+        <v>0.8038202386555893</v>
       </c>
       <c r="T94">
-        <v>10.26054051109287</v>
+        <v>11.72633201267757</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06416722104602272</v>
+        <v>0.06347725092724826</v>
       </c>
       <c r="W94">
-        <v>0.2206693692773479</v>
+        <v>0.2208320642313548</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3208361052301136</v>
+        <v>0.3173862546362414</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9172,22 +9172,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2616412364410513</v>
+        <v>0.2635412364410513</v>
       </c>
       <c r="C95">
-        <v>-29.08036846701362</v>
+        <v>-29.72246733734432</v>
       </c>
       <c r="D95">
-        <v>11.40749103169555</v>
+        <v>11.30794979038324</v>
       </c>
       <c r="E95">
-        <v>36.00209659687135</v>
+        <v>36.54465422588973</v>
       </c>
       <c r="F95">
-        <v>50.45785949870918</v>
+        <v>51.00041712772755</v>
       </c>
       <c r="G95">
         <v>9.970000000000001</v>
@@ -9208,37 +9208,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M95">
-        <v>11.89796326979562</v>
+        <v>12.02589835871816</v>
       </c>
       <c r="N95">
-        <v>-8.121713269795624</v>
+        <v>-8.249648358718156</v>
       </c>
       <c r="O95">
-        <v>-1.624342653959125</v>
+        <v>-1.649929671743631</v>
       </c>
       <c r="P95">
-        <v>-6.497370615836499</v>
+        <v>-6.599718686974525</v>
       </c>
       <c r="Q95">
-        <v>-4.5173706158365</v>
+        <v>-4.619718686974524</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8038202386555893</v>
+        <v>0.9301569450981879</v>
       </c>
       <c r="T95">
-        <v>11.72633201267757</v>
+        <v>13.68072068145717</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06347725092724826</v>
+        <v>0.06280196102376691</v>
       </c>
       <c r="W95">
-        <v>0.2208320642313548</v>
+        <v>0.2209912975905958</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3173862546362414</v>
+        <v>0.3140098051188346</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9254,22 +9254,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2635412364410513</v>
+        <v>0.2654412364410513</v>
       </c>
       <c r="C96">
-        <v>-29.72246733734432</v>
+        <v>-30.36284405056501</v>
       </c>
       <c r="D96">
-        <v>11.30794979038324</v>
+        <v>11.21013070618092</v>
       </c>
       <c r="E96">
-        <v>36.54465422588973</v>
+        <v>37.08721185490811</v>
       </c>
       <c r="F96">
-        <v>51.00041712772755</v>
+        <v>51.54297475674593</v>
       </c>
       <c r="G96">
         <v>9.970000000000001</v>
@@ -9290,37 +9290,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M96">
-        <v>12.02589835871816</v>
+        <v>12.15383344764069</v>
       </c>
       <c r="N96">
-        <v>-8.249648358718156</v>
+        <v>-8.37758344764069</v>
       </c>
       <c r="O96">
-        <v>-1.649929671743631</v>
+        <v>-1.675516689528138</v>
       </c>
       <c r="P96">
-        <v>-6.599718686974525</v>
+        <v>-6.702066758112553</v>
       </c>
       <c r="Q96">
-        <v>-4.619718686974524</v>
+        <v>-4.722066758112552</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9301569450981879</v>
+        <v>1.107028334117826</v>
       </c>
       <c r="T96">
-        <v>13.68072068145717</v>
+        <v>16.41686481774861</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06280196102376691</v>
+        <v>0.06214088774983252</v>
       </c>
       <c r="W96">
-        <v>0.2209912975905958</v>
+        <v>0.2211471786685895</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3140098051188346</v>
+        <v>0.3107044387491626</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9336,22 +9336,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2654412364410513</v>
+        <v>0.2673412364410513</v>
       </c>
       <c r="C97">
-        <v>-30.36284405056501</v>
+        <v>-31.00154291578801</v>
       </c>
       <c r="D97">
-        <v>11.21013070618092</v>
+        <v>11.1139894699763</v>
       </c>
       <c r="E97">
-        <v>37.08721185490811</v>
+        <v>37.62976948392649</v>
       </c>
       <c r="F97">
-        <v>51.54297475674593</v>
+        <v>52.08553238576431</v>
       </c>
       <c r="G97">
         <v>9.970000000000001</v>
@@ -9372,37 +9372,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M97">
-        <v>12.15383344764069</v>
+        <v>12.28176853656323</v>
       </c>
       <c r="N97">
-        <v>-8.37758344764069</v>
+        <v>-8.505518536563224</v>
       </c>
       <c r="O97">
-        <v>-1.675516689528138</v>
+        <v>-1.701103707312645</v>
       </c>
       <c r="P97">
-        <v>-6.702066758112553</v>
+        <v>-6.80441482925058</v>
       </c>
       <c r="Q97">
-        <v>-4.722066758112552</v>
+        <v>-4.82441482925058</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.107028334117826</v>
+        <v>1.372335417647283</v>
       </c>
       <c r="T97">
-        <v>16.41686481774861</v>
+        <v>20.52108102218577</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06214088774983252</v>
+        <v>0.06149358683577175</v>
       </c>
       <c r="W97">
-        <v>0.2211471786685895</v>
+        <v>0.221299812224125</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3107044387491626</v>
+        <v>0.3074679341788589</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9418,22 +9418,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2673412364410512</v>
+        <v>0.2692412364410512</v>
       </c>
       <c r="C98">
-        <v>-31.00154291578801</v>
+        <v>-31.63860673502131</v>
       </c>
       <c r="D98">
-        <v>11.1139894699763</v>
+        <v>11.01948327976138</v>
       </c>
       <c r="E98">
-        <v>37.62976948392648</v>
+        <v>38.17232711294486</v>
       </c>
       <c r="F98">
-        <v>52.0855323857643</v>
+        <v>52.62809001478269</v>
       </c>
       <c r="G98">
         <v>9.970000000000001</v>
@@ -9454,37 +9454,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M98">
-        <v>12.28176853656322</v>
+        <v>12.40970362548576</v>
       </c>
       <c r="N98">
-        <v>-8.505518536563223</v>
+        <v>-8.633453625485757</v>
       </c>
       <c r="O98">
-        <v>-1.701103707312645</v>
+        <v>-1.726690725097151</v>
       </c>
       <c r="P98">
-        <v>-6.804414829250578</v>
+        <v>-6.906762900388605</v>
       </c>
       <c r="Q98">
-        <v>-4.824414829250578</v>
+        <v>-4.926762900388605</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.37233541764728</v>
+        <v>1.814513890196373</v>
       </c>
       <c r="T98">
-        <v>20.52108102218572</v>
+        <v>27.3614413629143</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06149358683577177</v>
+        <v>0.0608596323323102</v>
       </c>
       <c r="W98">
-        <v>0.221299812224125</v>
+        <v>0.2214492986960413</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3074679341788589</v>
+        <v>0.304298161661551</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9500,22 +9500,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2692412364410512</v>
+        <v>0.2711412364410513</v>
       </c>
       <c r="C99">
-        <v>-31.63860673502131</v>
+        <v>-32.2740768667055</v>
       </c>
       <c r="D99">
-        <v>11.01948327976138</v>
+        <v>10.92657077709556</v>
       </c>
       <c r="E99">
-        <v>38.17232711294486</v>
+        <v>38.71488474196324</v>
       </c>
       <c r="F99">
-        <v>52.62809001478269</v>
+        <v>53.17064764380106</v>
       </c>
       <c r="G99">
         <v>9.970000000000001</v>
@@ -9536,37 +9536,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M99">
-        <v>12.40970362548576</v>
+        <v>12.53763871440829</v>
       </c>
       <c r="N99">
-        <v>-8.633453625485757</v>
+        <v>-8.761388714408289</v>
       </c>
       <c r="O99">
-        <v>-1.726690725097151</v>
+        <v>-1.752277742881658</v>
       </c>
       <c r="P99">
-        <v>-6.906762900388605</v>
+        <v>-7.009110971526631</v>
       </c>
       <c r="Q99">
-        <v>-4.926762900388605</v>
+        <v>-5.029110971526631</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.814513890196373</v>
+        <v>2.698870835294559</v>
       </c>
       <c r="T99">
-        <v>27.3614413629143</v>
+        <v>41.04216204437144</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0608596323323102</v>
+        <v>0.06023861567585806</v>
       </c>
       <c r="W99">
-        <v>0.2214492986960413</v>
+        <v>0.2215957344236327</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.304298161661551</v>
+        <v>0.3011930783792903</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9582,22 +9582,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2711412364410513</v>
+        <v>0.2730412364410513</v>
       </c>
       <c r="C100">
-        <v>-32.2740768667055</v>
+        <v>-32.90799328606327</v>
       </c>
       <c r="D100">
-        <v>10.92657077709556</v>
+        <v>10.83521198675617</v>
       </c>
       <c r="E100">
-        <v>38.71488474196324</v>
+        <v>39.25744237098162</v>
       </c>
       <c r="F100">
-        <v>53.17064764380106</v>
+        <v>53.71320527281944</v>
       </c>
       <c r="G100">
         <v>9.970000000000001</v>
@@ -9618,37 +9618,37 @@
         <v>3.776250000000001</v>
       </c>
       <c r="M100">
-        <v>12.53763871440829</v>
+        <v>12.66557380333083</v>
       </c>
       <c r="N100">
-        <v>-8.761388714408289</v>
+        <v>-8.889323803330825</v>
       </c>
       <c r="O100">
-        <v>-1.752277742881658</v>
+        <v>-1.777864760666165</v>
       </c>
       <c r="P100">
-        <v>-7.009110971526631</v>
+        <v>-7.11145904266466</v>
       </c>
       <c r="Q100">
-        <v>-5.029110971526631</v>
+        <v>-5.131459042664661</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.698870835294559</v>
+        <v>5.351941670589118</v>
       </c>
       <c r="T100">
-        <v>41.04216204437144</v>
+        <v>82.08432408874287</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06023861567585806</v>
+        <v>0.05963014481044535</v>
       </c>
       <c r="W100">
-        <v>0.2215957344236327</v>
+        <v>0.221739211853697</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9656,91 +9656,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3011930783792903</v>
+        <v>0.2981507240522268</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2730412364410513</v>
-      </c>
-      <c r="C101">
-        <v>-32.90799328606327</v>
-      </c>
-      <c r="D101">
-        <v>10.83521198675617</v>
-      </c>
-      <c r="E101">
-        <v>39.25744237098162</v>
-      </c>
-      <c r="F101">
-        <v>53.71320527281944</v>
-      </c>
-      <c r="G101">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="H101">
-        <v>39.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.756250000000001</v>
-      </c>
-      <c r="K101">
-        <v>1.98</v>
-      </c>
-      <c r="L101">
-        <v>3.776250000000001</v>
-      </c>
-      <c r="M101">
-        <v>12.66557380333083</v>
-      </c>
-      <c r="N101">
-        <v>-8.889323803330825</v>
-      </c>
-      <c r="O101">
-        <v>-1.777864760666165</v>
-      </c>
-      <c r="P101">
-        <v>-7.11145904266466</v>
-      </c>
-      <c r="Q101">
-        <v>-5.131459042664661</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.351941670589118</v>
-      </c>
-      <c r="T101">
-        <v>82.08432408874287</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05963014481044535</v>
-      </c>
-      <c r="W101">
-        <v>0.221739211853697</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2981507240522268</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
